--- a/forecast-results/河北电网披露及电价预估数据-20261018.xlsx
+++ b/forecast-results/河北电网披露及电价预估数据-20261018.xlsx
@@ -3764,25 +3764,25 @@
         <v>1</v>
       </c>
       <c r="D2" s="21" t="n">
-        <v>12739</v>
+        <v>12714</v>
       </c>
       <c r="E2" s="22" t="n">
-        <v>13170</v>
+        <v>13161</v>
       </c>
       <c r="F2" s="21" t="n">
-        <v>12196</v>
+        <v>12492</v>
       </c>
       <c r="G2" s="21" t="n">
-        <v>12259</v>
+        <v>12043</v>
       </c>
       <c r="H2" s="22" t="n">
-        <v>13043</v>
+        <v>12810</v>
       </c>
       <c r="I2" s="21" t="n">
-        <v>12601</v>
+        <v>12658</v>
       </c>
       <c r="J2" s="22" t="n">
-        <v>13121</v>
+        <v>13040</v>
       </c>
     </row>
     <row r="3">
@@ -3796,25 +3796,25 @@
         <v>1</v>
       </c>
       <c r="D3" s="21" t="n">
-        <v>12443</v>
+        <v>12440</v>
       </c>
       <c r="E3" s="22" t="n">
-        <v>12955</v>
+        <v>12946</v>
       </c>
       <c r="F3" s="21" t="n">
-        <v>12071</v>
+        <v>12447</v>
       </c>
       <c r="G3" s="21" t="n">
-        <v>12008</v>
+        <v>11886</v>
       </c>
       <c r="H3" s="22" t="n">
-        <v>12825</v>
+        <v>12561</v>
       </c>
       <c r="I3" s="21" t="n">
-        <v>12214</v>
+        <v>12176</v>
       </c>
       <c r="J3" s="22" t="n">
-        <v>12512</v>
+        <v>12514</v>
       </c>
     </row>
     <row r="4">
@@ -3828,25 +3828,25 @@
         <v>1</v>
       </c>
       <c r="D4" s="21" t="n">
-        <v>12284</v>
+        <v>12346</v>
       </c>
       <c r="E4" s="22" t="n">
-        <v>12857</v>
+        <v>12849</v>
       </c>
       <c r="F4" s="21" t="n">
-        <v>11946</v>
+        <v>12532</v>
       </c>
       <c r="G4" s="21" t="n">
-        <v>11957</v>
+        <v>11835</v>
       </c>
       <c r="H4" s="22" t="n">
-        <v>12710</v>
+        <v>12480</v>
       </c>
       <c r="I4" s="21" t="n">
-        <v>11921</v>
+        <v>11936</v>
       </c>
       <c r="J4" s="22" t="n">
-        <v>12223</v>
+        <v>12328</v>
       </c>
     </row>
     <row r="5">
@@ -3860,25 +3860,25 @@
         <v>1</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>12273</v>
+        <v>12300</v>
       </c>
       <c r="E5" s="22" t="n">
-        <v>12764</v>
+        <v>12756</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>12022</v>
+        <v>12418</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>11901</v>
+        <v>11797</v>
       </c>
       <c r="H5" s="22" t="n">
-        <v>12711</v>
+        <v>12452</v>
       </c>
       <c r="I5" s="21" t="n">
-        <v>11867</v>
+        <v>11896</v>
       </c>
       <c r="J5" s="22" t="n">
-        <v>12299</v>
+        <v>12383</v>
       </c>
     </row>
     <row r="6">
@@ -3892,25 +3892,25 @@
         <v>2</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>12226</v>
+        <v>12216</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>12701</v>
+        <v>12691</v>
       </c>
       <c r="F6" s="21" t="n">
-        <v>12051</v>
+        <v>12409</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>11844</v>
+        <v>11739</v>
       </c>
       <c r="H6" s="22" t="n">
-        <v>12516</v>
+        <v>12196</v>
       </c>
       <c r="I6" s="21" t="n">
-        <v>11898</v>
+        <v>11938</v>
       </c>
       <c r="J6" s="22" t="n">
-        <v>12262</v>
+        <v>12205</v>
       </c>
     </row>
     <row r="7">
@@ -3924,25 +3924,25 @@
         <v>2</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>12237</v>
+        <v>12218</v>
       </c>
       <c r="E7" s="22" t="n">
-        <v>12613</v>
+        <v>12603</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>12073</v>
+        <v>12402</v>
       </c>
       <c r="G7" s="21" t="n">
-        <v>11859</v>
+        <v>11755</v>
       </c>
       <c r="H7" s="22" t="n">
-        <v>12456</v>
+        <v>12146</v>
       </c>
       <c r="I7" s="21" t="n">
-        <v>11849</v>
+        <v>11887</v>
       </c>
       <c r="J7" s="22" t="n">
-        <v>12504</v>
+        <v>12415</v>
       </c>
     </row>
     <row r="8">
@@ -3956,25 +3956,25 @@
         <v>2</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>12166</v>
+        <v>12148</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>12497</v>
+        <v>12487</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>11915</v>
+        <v>12238</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>11738</v>
+        <v>11634</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>12384</v>
+        <v>12023</v>
       </c>
       <c r="I8" s="21" t="n">
-        <v>11890</v>
+        <v>11984</v>
       </c>
       <c r="J8" s="22" t="n">
-        <v>12529</v>
+        <v>12437</v>
       </c>
     </row>
     <row r="9">
@@ -3988,22 +3988,22 @@
         <v>2</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>12198</v>
+        <v>12190</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>12622</v>
+        <v>12614</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>12150</v>
+        <v>12438</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>11943</v>
+        <v>11839</v>
       </c>
       <c r="H9" s="22" t="n">
-        <v>12494</v>
+        <v>12141</v>
       </c>
       <c r="I9" s="21" t="n">
-        <v>11784</v>
+        <v>11875</v>
       </c>
       <c r="J9" s="22" t="n">
         <v>12115</v>
@@ -4020,25 +4020,25 @@
         <v>3</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>13789</v>
+        <v>13759</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>13782</v>
+        <v>13776</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>14028</v>
+        <v>13730</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>14193</v>
+        <v>14302</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>13739</v>
+        <v>13448</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>13195</v>
+        <v>13317</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>13752</v>
+        <v>13926</v>
       </c>
     </row>
     <row r="11">
@@ -4052,25 +4052,25 @@
         <v>3</v>
       </c>
       <c r="D11" s="21" t="n">
-        <v>13802</v>
+        <v>13752</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>13944</v>
+        <v>13933</v>
       </c>
       <c r="F11" s="21" t="n">
-        <v>13862</v>
+        <v>13631</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>14202</v>
+        <v>14277</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>13756</v>
+        <v>13449</v>
       </c>
       <c r="I11" s="21" t="n">
-        <v>12962</v>
+        <v>13098</v>
       </c>
       <c r="J11" s="22" t="n">
-        <v>14011</v>
+        <v>14026</v>
       </c>
     </row>
     <row r="12">
@@ -4084,25 +4084,25 @@
         <v>3</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>13692</v>
+        <v>13643</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>13790</v>
+        <v>13779</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>13500</v>
+        <v>13409</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>14168</v>
+        <v>14243</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>13635</v>
+        <v>13306</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>12865</v>
+        <v>12911</v>
       </c>
       <c r="J12" s="22" t="n">
-        <v>14139</v>
+        <v>14123</v>
       </c>
     </row>
     <row r="13">
@@ -4116,25 +4116,25 @@
         <v>3</v>
       </c>
       <c r="D13" s="21" t="n">
-        <v>13086</v>
+        <v>13042</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>13587</v>
+        <v>13574</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>12998</v>
+        <v>13049</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>12832</v>
+        <v>12746</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>13162</v>
+        <v>12946</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>12074</v>
+        <v>12229</v>
       </c>
       <c r="J13" s="22" t="n">
-        <v>13737</v>
+        <v>13560</v>
       </c>
     </row>
     <row r="14">
@@ -4148,25 +4148,25 @@
         <v>4</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>12691</v>
+        <v>12666</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>13496</v>
+        <v>13483</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>12648</v>
+        <v>12836</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>12503</v>
+        <v>12381</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>13046</v>
+        <v>12801</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>11895</v>
+        <v>11965</v>
       </c>
       <c r="J14" s="22" t="n">
-        <v>12370</v>
+        <v>12320</v>
       </c>
     </row>
     <row r="15">
@@ -4180,25 +4180,25 @@
         <v>4</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>12682</v>
+        <v>12686</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>13467</v>
+        <v>13454</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>12597</v>
+        <v>12901</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>12612</v>
+        <v>12490</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>12943</v>
+        <v>12714</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>11918</v>
+        <v>12028</v>
       </c>
       <c r="J15" s="22" t="n">
-        <v>12359</v>
+        <v>12313</v>
       </c>
     </row>
     <row r="16">
@@ -4212,25 +4212,25 @@
         <v>4</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>12679</v>
+        <v>12698</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>13463</v>
+        <v>13450</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>12654</v>
+        <v>12977</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>12532</v>
+        <v>12451</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>12917</v>
+        <v>12657</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>11930</v>
+        <v>12078</v>
       </c>
       <c r="J16" s="22" t="n">
-        <v>12384</v>
+        <v>12361</v>
       </c>
     </row>
     <row r="17">
@@ -4244,25 +4244,25 @@
         <v>4</v>
       </c>
       <c r="D17" s="21" t="n">
-        <v>12654</v>
+        <v>12677</v>
       </c>
       <c r="E17" s="22" t="n">
-        <v>13416</v>
+        <v>13403</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>12467</v>
+        <v>13004</v>
       </c>
       <c r="G17" s="21" t="n">
-        <v>12459</v>
+        <v>12378</v>
       </c>
       <c r="H17" s="22" t="n">
-        <v>12891</v>
+        <v>12611</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>12072</v>
+        <v>12151</v>
       </c>
       <c r="J17" s="22" t="n">
-        <v>12441</v>
+        <v>12312</v>
       </c>
     </row>
     <row r="18">
@@ -4276,25 +4276,25 @@
         <v>5</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>12680</v>
+        <v>12742</v>
       </c>
       <c r="E18" s="22" t="n">
-        <v>13465</v>
+        <v>13451</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>12531</v>
+        <v>13153</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>12408</v>
+        <v>12327</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>12893</v>
+        <v>12622</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>12094</v>
+        <v>12196</v>
       </c>
       <c r="J18" s="22" t="n">
-        <v>12507</v>
+        <v>12501</v>
       </c>
     </row>
     <row r="19">
@@ -4308,25 +4308,25 @@
         <v>5</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>12710</v>
+        <v>12783</v>
       </c>
       <c r="E19" s="22" t="n">
-        <v>13484</v>
+        <v>13471</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>12602</v>
+        <v>13272</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>12435</v>
+        <v>12354</v>
       </c>
       <c r="H19" s="22" t="n">
-        <v>12893</v>
+        <v>12622</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>12138</v>
+        <v>12254</v>
       </c>
       <c r="J19" s="22" t="n">
-        <v>12525</v>
+        <v>12519</v>
       </c>
     </row>
     <row r="20">
@@ -4340,25 +4340,25 @@
         <v>5</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>12737</v>
+        <v>12818</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>13502</v>
+        <v>13488</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>12601</v>
+        <v>13233</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>12437</v>
+        <v>12356</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>13053</v>
+        <v>12780</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>12148</v>
+        <v>12267</v>
       </c>
       <c r="J20" s="22" t="n">
-        <v>12516</v>
+        <v>12596</v>
       </c>
     </row>
     <row r="21">
@@ -4372,25 +4372,25 @@
         <v>5</v>
       </c>
       <c r="D21" s="21" t="n">
-        <v>13033</v>
+        <v>13107</v>
       </c>
       <c r="E21" s="22" t="n">
-        <v>13602</v>
+        <v>13591</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>12804</v>
+        <v>13415</v>
       </c>
       <c r="G21" s="21" t="n">
         <v>12835</v>
       </c>
       <c r="H21" s="22" t="n">
-        <v>13160</v>
+        <v>12863</v>
       </c>
       <c r="I21" s="21" t="n">
-        <v>12573</v>
+        <v>12685</v>
       </c>
       <c r="J21" s="22" t="n">
-        <v>13094</v>
+        <v>13101</v>
       </c>
     </row>
     <row r="22">
@@ -4404,25 +4404,25 @@
         <v>6</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>13696</v>
+        <v>13746</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>13834</v>
+        <v>13823</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>13077</v>
+        <v>13601</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>14185</v>
+        <v>14294</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>13628</v>
+        <v>13212</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>13449</v>
+        <v>13480</v>
       </c>
       <c r="J22" s="22" t="n">
-        <v>13964</v>
+        <v>13979</v>
       </c>
     </row>
     <row r="23">
@@ -4436,25 +4436,25 @@
         <v>6</v>
       </c>
       <c r="D23" s="21" t="n">
-        <v>13943</v>
+        <v>13896</v>
       </c>
       <c r="E23" s="22" t="n">
-        <v>13977</v>
+        <v>13966</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>13543</v>
+        <v>13693</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>14219</v>
+        <v>14294</v>
       </c>
       <c r="H23" s="22" t="n">
+        <v>13288</v>
+      </c>
+      <c r="I23" s="21" t="n">
         <v>13740</v>
       </c>
-      <c r="I23" s="21" t="n">
-        <v>13836</v>
-      </c>
       <c r="J23" s="22" t="n">
-        <v>14322</v>
+        <v>14314</v>
       </c>
     </row>
     <row r="24">
@@ -4468,25 +4468,25 @@
         <v>6</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>14063</v>
+        <v>14016</v>
       </c>
       <c r="E24" s="22" t="n">
-        <v>14119</v>
+        <v>14110</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>13582</v>
+        <v>13798</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>14354</v>
+        <v>14431</v>
       </c>
       <c r="H24" s="22" t="n">
-        <v>13898</v>
+        <v>13567</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>14011</v>
+        <v>13831</v>
       </c>
       <c r="J24" s="22" t="n">
-        <v>14395</v>
+        <v>14282</v>
       </c>
     </row>
     <row r="25">
@@ -4500,25 +4500,25 @@
         <v>6</v>
       </c>
       <c r="D25" s="21" t="n">
-        <v>14161</v>
+        <v>14108</v>
       </c>
       <c r="E25" s="22" t="n">
-        <v>14227</v>
+        <v>14218</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>13666</v>
+        <v>13772</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>14354</v>
+        <v>14431</v>
       </c>
       <c r="H25" s="22" t="n">
-        <v>14075</v>
+        <v>13699</v>
       </c>
       <c r="I25" s="21" t="n">
-        <v>14169</v>
+        <v>14078</v>
       </c>
       <c r="J25" s="22" t="n">
-        <v>14466</v>
+        <v>14380</v>
       </c>
     </row>
     <row r="26">
@@ -4532,25 +4532,25 @@
         <v>7</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>14236</v>
+        <v>14196</v>
       </c>
       <c r="E26" s="22" t="n">
-        <v>13992</v>
+        <v>13986</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>13696</v>
+        <v>13804</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>14371</v>
+        <v>14449</v>
       </c>
       <c r="H26" s="22" t="n">
-        <v>14349</v>
+        <v>14118</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>14399</v>
+        <v>14279</v>
       </c>
       <c r="J26" s="22" t="n">
-        <v>14703</v>
+        <v>14594</v>
       </c>
     </row>
     <row r="27">
@@ -4564,25 +4564,25 @@
         <v>7</v>
       </c>
       <c r="D27" s="21" t="n">
-        <v>14703</v>
+        <v>14738</v>
       </c>
       <c r="E27" s="22" t="n">
-        <v>14317</v>
+        <v>14314</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>14267</v>
+        <v>14809</v>
       </c>
       <c r="G27" s="21" t="n">
-        <v>14699</v>
+        <v>14726</v>
       </c>
       <c r="H27" s="22" t="n">
-        <v>14998</v>
+        <v>14770</v>
       </c>
       <c r="I27" s="21" t="n">
-        <v>15020</v>
+        <v>14954</v>
       </c>
       <c r="J27" s="22" t="n">
-        <v>15072</v>
+        <v>14976</v>
       </c>
     </row>
     <row r="28">
@@ -4596,25 +4596,25 @@
         <v>7</v>
       </c>
       <c r="D28" s="21" t="n">
-        <v>14943</v>
+        <v>14932</v>
       </c>
       <c r="E28" s="22" t="n">
-        <v>14562</v>
+        <v>14559</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>14643</v>
+        <v>14861</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>14705</v>
+        <v>14731</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>15332</v>
+        <v>15072</v>
       </c>
       <c r="I28" s="21" t="n">
-        <v>15186</v>
+        <v>15237</v>
       </c>
       <c r="J28" s="22" t="n">
-        <v>15390</v>
+        <v>15256</v>
       </c>
     </row>
     <row r="29">
@@ -4628,25 +4628,25 @@
         <v>7</v>
       </c>
       <c r="D29" s="21" t="n">
-        <v>15087</v>
+        <v>15124</v>
       </c>
       <c r="E29" s="22" t="n">
-        <v>14638</v>
+        <v>14635</v>
       </c>
       <c r="F29" s="21" t="n">
-        <v>14768</v>
+        <v>15070</v>
       </c>
       <c r="G29" s="21" t="n">
-        <v>14885</v>
+        <v>14884</v>
       </c>
       <c r="H29" s="22" t="n">
-        <v>15499</v>
+        <v>15242</v>
       </c>
       <c r="I29" s="21" t="n">
-        <v>15451</v>
+        <v>15520</v>
       </c>
       <c r="J29" s="22" t="n">
-        <v>15462</v>
+        <v>15554</v>
       </c>
     </row>
     <row r="30">
@@ -4660,25 +4660,25 @@
         <v>8</v>
       </c>
       <c r="D30" s="21" t="n">
-        <v>14956</v>
+        <v>15006</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>14615</v>
+        <v>14610</v>
       </c>
       <c r="F30" s="21" t="n">
-        <v>14697</v>
+        <v>15138</v>
       </c>
       <c r="G30" s="21" t="n">
-        <v>14908</v>
+        <v>14934</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>15354</v>
+        <v>15128</v>
       </c>
       <c r="I30" s="21" t="n">
-        <v>15186</v>
+        <v>15251</v>
       </c>
       <c r="J30" s="22" t="n">
-        <v>15121</v>
+        <v>15095</v>
       </c>
     </row>
     <row r="31">
@@ -4692,25 +4692,25 @@
         <v>8</v>
       </c>
       <c r="D31" s="21" t="n">
-        <v>14629</v>
+        <v>14727</v>
       </c>
       <c r="E31" s="22" t="n">
-        <v>14255</v>
+        <v>14246</v>
       </c>
       <c r="F31" s="21" t="n">
-        <v>14127</v>
+        <v>14712</v>
       </c>
       <c r="G31" s="21" t="n">
-        <v>14656</v>
+        <v>14780</v>
       </c>
       <c r="H31" s="22" t="n">
-        <v>14892</v>
+        <v>14685</v>
       </c>
       <c r="I31" s="21" t="n">
-        <v>14874</v>
+        <v>15006</v>
       </c>
       <c r="J31" s="22" t="n">
-        <v>15122</v>
+        <v>15065</v>
       </c>
     </row>
     <row r="32">
@@ -4724,25 +4724,25 @@
         <v>8</v>
       </c>
       <c r="D32" s="21" t="n">
-        <v>14094</v>
+        <v>14161</v>
       </c>
       <c r="E32" s="22" t="n">
-        <v>13792</v>
+        <v>13782</v>
       </c>
       <c r="F32" s="21" t="n">
-        <v>13849</v>
+        <v>14149</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>14315</v>
+        <v>14390</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>14275</v>
+        <v>14053</v>
       </c>
       <c r="I32" s="21" t="n">
-        <v>13909</v>
+        <v>14151</v>
       </c>
       <c r="J32" s="22" t="n">
-        <v>14518</v>
+        <v>14528</v>
       </c>
     </row>
     <row r="33">
@@ -4756,25 +4756,25 @@
         <v>8</v>
       </c>
       <c r="D33" s="21" t="n">
-        <v>14040</v>
+        <v>14000</v>
       </c>
       <c r="E33" s="22" t="n">
-        <v>13523</v>
+        <v>13513</v>
       </c>
       <c r="F33" s="21" t="n">
-        <v>13940</v>
+        <v>13761</v>
       </c>
       <c r="G33" s="21" t="n">
-        <v>14431</v>
+        <v>14506</v>
       </c>
       <c r="H33" s="22" t="n">
-        <v>14091</v>
+        <v>13831</v>
       </c>
       <c r="I33" s="21" t="n">
-        <v>13702</v>
+        <v>13796</v>
       </c>
       <c r="J33" s="22" t="n">
-        <v>14675</v>
+        <v>14698</v>
       </c>
     </row>
     <row r="34">
@@ -4788,25 +4788,25 @@
         <v>9</v>
       </c>
       <c r="D34" s="21" t="n">
-        <v>13484</v>
+        <v>13475</v>
       </c>
       <c r="E34" s="22" t="n">
-        <v>13107</v>
+        <v>13094</v>
       </c>
       <c r="F34" s="21" t="n">
-        <v>13822</v>
+        <v>13253</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>13653</v>
+        <v>13869</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>13098</v>
+        <v>12932</v>
       </c>
       <c r="I34" s="21" t="n">
-        <v>13042</v>
+        <v>13299</v>
       </c>
       <c r="J34" s="22" t="n">
-        <v>14216</v>
+        <v>14454</v>
       </c>
     </row>
     <row r="35">
@@ -4820,25 +4820,25 @@
         <v>9</v>
       </c>
       <c r="D35" s="21" t="n">
-        <v>12781</v>
+        <v>12832</v>
       </c>
       <c r="E35" s="22" t="n">
-        <v>12610</v>
+        <v>12596</v>
       </c>
       <c r="F35" s="21" t="n">
-        <v>13402</v>
+        <v>12951</v>
       </c>
       <c r="G35" s="21" t="n">
-        <v>12692</v>
+        <v>13098</v>
       </c>
       <c r="H35" s="22" t="n">
-        <v>12517</v>
+        <v>12394</v>
       </c>
       <c r="I35" s="21" t="n">
-        <v>12050</v>
+        <v>12312</v>
       </c>
       <c r="J35" s="22" t="n">
-        <v>13396</v>
+        <v>13647</v>
       </c>
     </row>
     <row r="36">
@@ -4852,25 +4852,25 @@
         <v>9</v>
       </c>
       <c r="D36" s="21" t="n">
-        <v>11990</v>
+        <v>11974</v>
       </c>
       <c r="E36" s="22" t="n">
-        <v>11948</v>
+        <v>11932</v>
       </c>
       <c r="F36" s="21" t="n">
-        <v>12148</v>
+        <v>11779</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>11646</v>
+        <v>11679</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>11871</v>
+        <v>11827</v>
       </c>
       <c r="I36" s="21" t="n">
-        <v>11271</v>
+        <v>11415</v>
       </c>
       <c r="J36" s="22" t="n">
-        <v>13051</v>
+        <v>13228</v>
       </c>
     </row>
     <row r="37">
@@ -4884,25 +4884,25 @@
         <v>9</v>
       </c>
       <c r="D37" s="21" t="n">
-        <v>11567</v>
+        <v>11542</v>
       </c>
       <c r="E37" s="22" t="n">
-        <v>11361</v>
+        <v>11344</v>
       </c>
       <c r="F37" s="21" t="n">
-        <v>11743</v>
+        <v>11349</v>
       </c>
       <c r="G37" s="21" t="n">
-        <v>10910</v>
+        <v>10986</v>
       </c>
       <c r="H37" s="22" t="n">
-        <v>11646</v>
+        <v>11533</v>
       </c>
       <c r="I37" s="21" t="n">
-        <v>11096</v>
+        <v>11232</v>
       </c>
       <c r="J37" s="22" t="n">
-        <v>12721</v>
+        <v>12889</v>
       </c>
     </row>
     <row r="38">
@@ -4916,25 +4916,25 @@
         <v>10</v>
       </c>
       <c r="D38" s="21" t="n">
-        <v>10954</v>
+        <v>10945</v>
       </c>
       <c r="E38" s="22" t="n">
-        <v>10832</v>
+        <v>10811</v>
       </c>
       <c r="F38" s="21" t="n">
-        <v>11286</v>
+        <v>10864</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>10502</v>
+        <v>10578</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>10834</v>
+        <v>10812</v>
       </c>
       <c r="I38" s="21" t="n">
-        <v>10732</v>
+        <v>10788</v>
       </c>
       <c r="J38" s="22" t="n">
-        <v>11558</v>
+        <v>11860</v>
       </c>
     </row>
     <row r="39">
@@ -4948,25 +4948,25 @@
         <v>10</v>
       </c>
       <c r="D39" s="21" t="n">
-        <v>10428</v>
+        <v>10412</v>
       </c>
       <c r="E39" s="22" t="n">
-        <v>10277</v>
+        <v>10257</v>
       </c>
       <c r="F39" s="21" t="n">
-        <v>10336</v>
+        <v>10160</v>
       </c>
       <c r="G39" s="21" t="n">
-        <v>10376</v>
+        <v>10432</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>10529</v>
+        <v>10419</v>
       </c>
       <c r="I39" s="21" t="n">
-        <v>10407</v>
+        <v>10422</v>
       </c>
       <c r="J39" s="22" t="n">
-        <v>10700</v>
+        <v>10830</v>
       </c>
     </row>
     <row r="40">
@@ -4980,25 +4980,25 @@
         <v>10</v>
       </c>
       <c r="D40" s="21" t="n">
-        <v>10041</v>
+        <v>10070</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>9914</v>
+        <v>9893</v>
       </c>
       <c r="F40" s="21" t="n">
-        <v>9718</v>
+        <v>9748</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>9930</v>
+        <v>9951</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>10301</v>
+        <v>10278</v>
       </c>
       <c r="I40" s="21" t="n">
-        <v>10215</v>
+        <v>10184</v>
       </c>
       <c r="J40" s="22" t="n">
-        <v>10246</v>
+        <v>10449</v>
       </c>
     </row>
     <row r="41">
@@ -5012,25 +5012,25 @@
         <v>10</v>
       </c>
       <c r="D41" s="21" t="n">
-        <v>9941</v>
+        <v>10000</v>
       </c>
       <c r="E41" s="22" t="n">
-        <v>9594</v>
+        <v>9572</v>
       </c>
       <c r="F41" s="21" t="n">
-        <v>9463</v>
+        <v>9670</v>
       </c>
       <c r="G41" s="21" t="n">
-        <v>10068</v>
+        <v>10029</v>
       </c>
       <c r="H41" s="22" t="n">
-        <v>10207</v>
+        <v>10208</v>
       </c>
       <c r="I41" s="21" t="n">
-        <v>10224</v>
+        <v>10234</v>
       </c>
       <c r="J41" s="22" t="n">
-        <v>10232</v>
+        <v>10435</v>
       </c>
     </row>
     <row r="42">
@@ -5044,25 +5044,25 @@
         <v>11</v>
       </c>
       <c r="D42" s="21" t="n">
-        <v>9940</v>
+        <v>9969</v>
       </c>
       <c r="E42" s="22" t="n">
-        <v>9439</v>
+        <v>9416</v>
       </c>
       <c r="F42" s="21" t="n">
-        <v>9580</v>
+        <v>9666</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>10340</v>
+        <v>10321</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>9908</v>
+        <v>9847</v>
       </c>
       <c r="I42" s="21" t="n">
-        <v>10277</v>
+        <v>10307</v>
       </c>
       <c r="J42" s="22" t="n">
-        <v>10232</v>
+        <v>10397</v>
       </c>
     </row>
     <row r="43">
@@ -5076,25 +5076,25 @@
         <v>11</v>
       </c>
       <c r="D43" s="21" t="n">
-        <v>9891</v>
+        <v>9910</v>
       </c>
       <c r="E43" s="22" t="n">
-        <v>9247</v>
+        <v>9224</v>
       </c>
       <c r="F43" s="21" t="n">
-        <v>9585</v>
+        <v>9609</v>
       </c>
       <c r="G43" s="21" t="n">
-        <v>10302</v>
+        <v>10284</v>
       </c>
       <c r="H43" s="22" t="n">
-        <v>9888</v>
+        <v>9828</v>
       </c>
       <c r="I43" s="21" t="n">
-        <v>10275</v>
+        <v>10303</v>
       </c>
       <c r="J43" s="22" t="n">
-        <v>10223</v>
+        <v>10393</v>
       </c>
     </row>
     <row r="44">
@@ -5108,25 +5108,25 @@
         <v>11</v>
       </c>
       <c r="D44" s="21" t="n">
-        <v>9878</v>
+        <v>9897</v>
       </c>
       <c r="E44" s="22" t="n">
-        <v>9115</v>
+        <v>9093</v>
       </c>
       <c r="F44" s="21" t="n">
-        <v>9734</v>
+        <v>9745</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>10325</v>
+        <v>10306</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>9893</v>
+        <v>9836</v>
       </c>
       <c r="I44" s="21" t="n">
-        <v>10240</v>
+        <v>10257</v>
       </c>
       <c r="J44" s="22" t="n">
-        <v>10162</v>
+        <v>10348</v>
       </c>
     </row>
     <row r="45">
@@ -5140,25 +5140,25 @@
         <v>11</v>
       </c>
       <c r="D45" s="21" t="n">
-        <v>9869</v>
+        <v>9891</v>
       </c>
       <c r="E45" s="22" t="n">
-        <v>9068</v>
+        <v>9045</v>
       </c>
       <c r="F45" s="21" t="n">
-        <v>9742</v>
+        <v>9735</v>
       </c>
       <c r="G45" s="21" t="n">
-        <v>10352</v>
+        <v>10334</v>
       </c>
       <c r="H45" s="22" t="n">
-        <v>9917</v>
+        <v>9892</v>
       </c>
       <c r="I45" s="21" t="n">
-        <v>10199</v>
+        <v>10241</v>
       </c>
       <c r="J45" s="22" t="n">
-        <v>10146</v>
+        <v>10322</v>
       </c>
     </row>
     <row r="46">
@@ -5172,25 +5172,25 @@
         <v>12</v>
       </c>
       <c r="D46" s="21" t="n">
-        <v>10691</v>
+        <v>10758</v>
       </c>
       <c r="E46" s="22" t="n">
-        <v>9940</v>
+        <v>9919</v>
       </c>
       <c r="F46" s="21" t="n">
-        <v>10596</v>
+        <v>10687</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>11052</v>
+        <v>11008</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>10468</v>
+        <v>10402</v>
       </c>
       <c r="I46" s="21" t="n">
-        <v>10789</v>
+        <v>10924</v>
       </c>
       <c r="J46" s="22" t="n">
-        <v>11472</v>
+        <v>11801</v>
       </c>
     </row>
     <row r="47">
@@ -5204,25 +5204,25 @@
         <v>12</v>
       </c>
       <c r="D47" s="21" t="n">
-        <v>10514</v>
+        <v>10492</v>
       </c>
       <c r="E47" s="22" t="n">
-        <v>10066</v>
+        <v>10043</v>
       </c>
       <c r="F47" s="21" t="n">
-        <v>10464</v>
+        <v>10368</v>
       </c>
       <c r="G47" s="21" t="n">
-        <v>10828</v>
+        <v>10826</v>
       </c>
       <c r="H47" s="22" t="n">
-        <v>10352</v>
+        <v>10218</v>
       </c>
       <c r="I47" s="21" t="n">
-        <v>10509</v>
+        <v>10631</v>
       </c>
       <c r="J47" s="22" t="n">
-        <v>10960</v>
+        <v>10956</v>
       </c>
     </row>
     <row r="48">
@@ -5236,25 +5236,25 @@
         <v>12</v>
       </c>
       <c r="D48" s="21" t="n">
-        <v>10242</v>
+        <v>10218</v>
       </c>
       <c r="E48" s="22" t="n">
-        <v>10000</v>
+        <v>9978</v>
       </c>
       <c r="F48" s="21" t="n">
-        <v>10102</v>
+        <v>9943</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>10538</v>
+        <v>10519</v>
       </c>
       <c r="H48" s="22" t="n">
-        <v>10104</v>
+        <v>10031</v>
       </c>
       <c r="I48" s="21" t="n">
-        <v>10347</v>
+        <v>10430</v>
       </c>
       <c r="J48" s="22" t="n">
-        <v>10409</v>
+        <v>10451</v>
       </c>
     </row>
     <row r="49">
@@ -5268,25 +5268,25 @@
         <v>12</v>
       </c>
       <c r="D49" s="21" t="n">
-        <v>9982</v>
+        <v>9987</v>
       </c>
       <c r="E49" s="22" t="n">
-        <v>9706</v>
+        <v>9682</v>
       </c>
       <c r="F49" s="21" t="n">
-        <v>9640</v>
+        <v>9681</v>
       </c>
       <c r="G49" s="21" t="n">
-        <v>10293</v>
+        <v>10267</v>
       </c>
       <c r="H49" s="22" t="n">
-        <v>9909</v>
+        <v>9824</v>
       </c>
       <c r="I49" s="21" t="n">
-        <v>10104</v>
+        <v>10245</v>
       </c>
       <c r="J49" s="22" t="n">
-        <v>10314</v>
+        <v>10295</v>
       </c>
     </row>
     <row r="50">
@@ -5300,25 +5300,25 @@
         <v>13</v>
       </c>
       <c r="D50" s="21" t="n">
-        <v>9820</v>
+        <v>9808</v>
       </c>
       <c r="E50" s="22" t="n">
-        <v>9771</v>
+        <v>9749</v>
       </c>
       <c r="F50" s="21" t="n">
-        <v>9465</v>
+        <v>9575</v>
       </c>
       <c r="G50" s="21" t="n">
-        <v>9935</v>
+        <v>9896</v>
       </c>
       <c r="H50" s="22" t="n">
-        <v>9839</v>
+        <v>9678</v>
       </c>
       <c r="I50" s="21" t="n">
-        <v>9895</v>
+        <v>9952</v>
       </c>
       <c r="J50" s="22" t="n">
-        <v>10044</v>
+        <v>10009</v>
       </c>
     </row>
     <row r="51">
@@ -5332,25 +5332,25 @@
         <v>13</v>
       </c>
       <c r="D51" s="21" t="n">
-        <v>9781</v>
+        <v>9790</v>
       </c>
       <c r="E51" s="22" t="n">
-        <v>9838</v>
+        <v>9815</v>
       </c>
       <c r="F51" s="21" t="n">
-        <v>9422</v>
+        <v>9508</v>
       </c>
       <c r="G51" s="21" t="n">
-        <v>9794</v>
+        <v>9768</v>
       </c>
       <c r="H51" s="22" t="n">
-        <v>9819</v>
+        <v>9685</v>
       </c>
       <c r="I51" s="21" t="n">
-        <v>9865</v>
+        <v>9919</v>
       </c>
       <c r="J51" s="22" t="n">
-        <v>9957</v>
+        <v>10041</v>
       </c>
     </row>
     <row r="52">
@@ -5364,25 +5364,25 @@
         <v>13</v>
       </c>
       <c r="D52" s="21" t="n">
-        <v>9835</v>
+        <v>9846</v>
       </c>
       <c r="E52" s="22" t="n">
-        <v>9903</v>
+        <v>9881</v>
       </c>
       <c r="F52" s="21" t="n">
-        <v>9415</v>
+        <v>9547</v>
       </c>
       <c r="G52" s="21" t="n">
-        <v>9761</v>
+        <v>9748</v>
       </c>
       <c r="H52" s="22" t="n">
-        <v>10136</v>
+        <v>9967</v>
       </c>
       <c r="I52" s="21" t="n">
-        <v>9847</v>
+        <v>9885</v>
       </c>
       <c r="J52" s="22" t="n">
-        <v>9977</v>
+        <v>10063</v>
       </c>
     </row>
     <row r="53">
@@ -5396,25 +5396,25 @@
         <v>13</v>
       </c>
       <c r="D53" s="21" t="n">
-        <v>9942</v>
+        <v>9945</v>
       </c>
       <c r="E53" s="22" t="n">
-        <v>10083</v>
+        <v>10062</v>
       </c>
       <c r="F53" s="21" t="n">
-        <v>9572</v>
+        <v>9675</v>
       </c>
       <c r="G53" s="21" t="n">
-        <v>9908</v>
+        <v>9882</v>
       </c>
       <c r="H53" s="22" t="n">
-        <v>10100</v>
+        <v>10005</v>
       </c>
       <c r="I53" s="21" t="n">
-        <v>9924</v>
+        <v>9987</v>
       </c>
       <c r="J53" s="22" t="n">
-        <v>10061</v>
+        <v>10041</v>
       </c>
     </row>
     <row r="54">
@@ -5428,25 +5428,25 @@
         <v>14</v>
       </c>
       <c r="D54" s="21" t="n">
-        <v>10211</v>
+        <v>10206</v>
       </c>
       <c r="E54" s="22" t="n">
-        <v>10504</v>
+        <v>10485</v>
       </c>
       <c r="F54" s="21" t="n">
-        <v>9818</v>
+        <v>9938</v>
       </c>
       <c r="G54" s="21" t="n">
-        <v>10454</v>
+        <v>10428</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>10206</v>
+        <v>10048</v>
       </c>
       <c r="I54" s="21" t="n">
-        <v>10061</v>
+        <v>10162</v>
       </c>
       <c r="J54" s="22" t="n">
-        <v>10152</v>
+        <v>10082</v>
       </c>
     </row>
     <row r="55">
@@ -5460,25 +5460,25 @@
         <v>14</v>
       </c>
       <c r="D55" s="21" t="n">
-        <v>10361</v>
+        <v>10415</v>
       </c>
       <c r="E55" s="22" t="n">
-        <v>10939</v>
+        <v>10922</v>
       </c>
       <c r="F55" s="21" t="n">
-        <v>9858</v>
+        <v>10170</v>
       </c>
       <c r="G55" s="21" t="n">
-        <v>10560</v>
+        <v>10534</v>
       </c>
       <c r="H55" s="22" t="n">
-        <v>10345</v>
+        <v>10199</v>
       </c>
       <c r="I55" s="21" t="n">
-        <v>10124</v>
+        <v>10260</v>
       </c>
       <c r="J55" s="22" t="n">
-        <v>10195</v>
+        <v>10253</v>
       </c>
     </row>
     <row r="56">
@@ -5492,25 +5492,25 @@
         <v>14</v>
       </c>
       <c r="D56" s="21" t="n">
-        <v>10860</v>
+        <v>10887</v>
       </c>
       <c r="E56" s="22" t="n">
-        <v>11355</v>
+        <v>11339</v>
       </c>
       <c r="F56" s="21" t="n">
-        <v>10373</v>
+        <v>10581</v>
       </c>
       <c r="G56" s="21" t="n">
-        <v>10665</v>
+        <v>10656</v>
       </c>
       <c r="H56" s="22" t="n">
-        <v>11207</v>
+        <v>11081</v>
       </c>
       <c r="I56" s="21" t="n">
-        <v>10522</v>
+        <v>10639</v>
       </c>
       <c r="J56" s="22" t="n">
-        <v>10964</v>
+        <v>10935</v>
       </c>
     </row>
     <row r="57">
@@ -5524,25 +5524,25 @@
         <v>14</v>
       </c>
       <c r="D57" s="21" t="n">
-        <v>11269</v>
+        <v>11318</v>
       </c>
       <c r="E57" s="22" t="n">
-        <v>11745</v>
+        <v>11730</v>
       </c>
       <c r="F57" s="21" t="n">
-        <v>10804</v>
+        <v>11343</v>
       </c>
       <c r="G57" s="21" t="n">
-        <v>10880</v>
+        <v>10859</v>
       </c>
       <c r="H57" s="22" t="n">
-        <v>11734</v>
+        <v>11439</v>
       </c>
       <c r="I57" s="21" t="n">
-        <v>10788</v>
+        <v>10942</v>
       </c>
       <c r="J57" s="22" t="n">
-        <v>11606</v>
+        <v>11511</v>
       </c>
     </row>
     <row r="58">
@@ -5556,25 +5556,25 @@
         <v>15</v>
       </c>
       <c r="D58" s="21" t="n">
-        <v>11722</v>
+        <v>11659</v>
       </c>
       <c r="E58" s="22" t="n">
-        <v>12198</v>
+        <v>12183</v>
       </c>
       <c r="F58" s="21" t="n">
-        <v>11980</v>
+        <v>11780</v>
       </c>
       <c r="G58" s="21" t="n">
-        <v>11096</v>
+        <v>11016</v>
       </c>
       <c r="H58" s="22" t="n">
-        <v>12251</v>
+        <v>11876</v>
       </c>
       <c r="I58" s="21" t="n">
-        <v>11079</v>
+        <v>11097</v>
       </c>
       <c r="J58" s="22" t="n">
-        <v>11647</v>
+        <v>11895</v>
       </c>
     </row>
     <row r="59">
@@ -5588,25 +5588,25 @@
         <v>15</v>
       </c>
       <c r="D59" s="21" t="n">
-        <v>12971</v>
+        <v>12906</v>
       </c>
       <c r="E59" s="22" t="n">
-        <v>12596</v>
+        <v>12583</v>
       </c>
       <c r="F59" s="21" t="n">
-        <v>12725</v>
+        <v>12359</v>
       </c>
       <c r="G59" s="21" t="n">
-        <v>13426</v>
+        <v>13489</v>
       </c>
       <c r="H59" s="22" t="n">
-        <v>12863</v>
+        <v>12495</v>
       </c>
       <c r="I59" s="21" t="n">
-        <v>12655</v>
+        <v>12869</v>
       </c>
       <c r="J59" s="22" t="n">
-        <v>13638</v>
+        <v>13688</v>
       </c>
     </row>
     <row r="60">
@@ -5620,25 +5620,25 @@
         <v>15</v>
       </c>
       <c r="D60" s="21" t="n">
-        <v>13399</v>
+        <v>13338</v>
       </c>
       <c r="E60" s="22" t="n">
-        <v>13006</v>
+        <v>12994</v>
       </c>
       <c r="F60" s="21" t="n">
-        <v>13474</v>
+        <v>13149</v>
       </c>
       <c r="G60" s="21" t="n">
-        <v>13510</v>
+        <v>13548</v>
       </c>
       <c r="H60" s="22" t="n">
-        <v>13478</v>
+        <v>13161</v>
       </c>
       <c r="I60" s="21" t="n">
-        <v>13334</v>
+        <v>13471</v>
       </c>
       <c r="J60" s="22" t="n">
-        <v>13696</v>
+        <v>13782</v>
       </c>
     </row>
     <row r="61">
@@ -5652,25 +5652,25 @@
         <v>15</v>
       </c>
       <c r="D61" s="21" t="n">
-        <v>13899</v>
+        <v>13836</v>
       </c>
       <c r="E61" s="22" t="n">
-        <v>13283</v>
+        <v>13270</v>
       </c>
       <c r="F61" s="21" t="n">
-        <v>14193</v>
+        <v>14060</v>
       </c>
       <c r="G61" s="21" t="n">
-        <v>13655</v>
+        <v>13720</v>
       </c>
       <c r="H61" s="22" t="n">
-        <v>13909</v>
+        <v>13592</v>
       </c>
       <c r="I61" s="21" t="n">
-        <v>14164</v>
+        <v>14277</v>
       </c>
       <c r="J61" s="22" t="n">
-        <v>14357</v>
+        <v>14230</v>
       </c>
     </row>
     <row r="62">
@@ -5684,25 +5684,25 @@
         <v>16</v>
       </c>
       <c r="D62" s="21" t="n">
-        <v>14247</v>
+        <v>14182</v>
       </c>
       <c r="E62" s="22" t="n">
-        <v>13294</v>
+        <v>13285</v>
       </c>
       <c r="F62" s="21" t="n">
-        <v>14184</v>
+        <v>14025</v>
       </c>
       <c r="G62" s="21" t="n">
-        <v>14048</v>
+        <v>14031</v>
       </c>
       <c r="H62" s="22" t="n">
-        <v>14409</v>
+        <v>14164</v>
       </c>
       <c r="I62" s="21" t="n">
-        <v>14863</v>
+        <v>15015</v>
       </c>
       <c r="J62" s="22" t="n">
-        <v>14976</v>
+        <v>14837</v>
       </c>
     </row>
     <row r="63">
@@ -5716,25 +5716,25 @@
         <v>16</v>
       </c>
       <c r="D63" s="21" t="n">
-        <v>14682</v>
+        <v>14690</v>
       </c>
       <c r="E63" s="22" t="n">
-        <v>13658</v>
+        <v>13648</v>
       </c>
       <c r="F63" s="21" t="n">
-        <v>15017</v>
+        <v>15140</v>
       </c>
       <c r="G63" s="21" t="n">
-        <v>14230</v>
+        <v>14185</v>
       </c>
       <c r="H63" s="22" t="n">
-        <v>14931</v>
+        <v>14761</v>
       </c>
       <c r="I63" s="21" t="n">
-        <v>15322</v>
+        <v>15471</v>
       </c>
       <c r="J63" s="22" t="n">
-        <v>15241</v>
+        <v>15238</v>
       </c>
     </row>
     <row r="64">
@@ -5748,25 +5748,25 @@
         <v>16</v>
       </c>
       <c r="D64" s="21" t="n">
-        <v>15374</v>
+        <v>15422</v>
       </c>
       <c r="E64" s="22" t="n">
-        <v>14092</v>
+        <v>14084</v>
       </c>
       <c r="F64" s="21" t="n">
-        <v>15729</v>
+        <v>16152</v>
       </c>
       <c r="G64" s="21" t="n">
-        <v>14362</v>
+        <v>14350</v>
       </c>
       <c r="H64" s="22" t="n">
-        <v>15864</v>
+        <v>15588</v>
       </c>
       <c r="I64" s="21" t="n">
-        <v>16437</v>
+        <v>16527</v>
       </c>
       <c r="J64" s="22" t="n">
-        <v>16185</v>
+        <v>16243</v>
       </c>
     </row>
     <row r="65">
@@ -5780,25 +5780,25 @@
         <v>16</v>
       </c>
       <c r="D65" s="21" t="n">
-        <v>16617</v>
+        <v>16611</v>
       </c>
       <c r="E65" s="22" t="n">
-        <v>14685</v>
+        <v>14679</v>
       </c>
       <c r="F65" s="21" t="n">
-        <v>16812</v>
+        <v>16807</v>
       </c>
       <c r="G65" s="21" t="n">
-        <v>16846</v>
+        <v>16885</v>
       </c>
       <c r="H65" s="22" t="n">
-        <v>17042</v>
+        <v>16700</v>
       </c>
       <c r="I65" s="21" t="n">
-        <v>17571</v>
+        <v>17851</v>
       </c>
       <c r="J65" s="22" t="n">
-        <v>17293</v>
+        <v>17269</v>
       </c>
     </row>
     <row r="66">
@@ -5812,25 +5812,25 @@
         <v>17</v>
       </c>
       <c r="D66" s="21" t="n">
-        <v>17061</v>
+        <v>17093</v>
       </c>
       <c r="E66" s="22" t="n">
-        <v>15125</v>
+        <v>15127</v>
       </c>
       <c r="F66" s="21" t="n">
-        <v>17332</v>
+        <v>17372</v>
       </c>
       <c r="G66" s="21" t="n">
-        <v>17262</v>
+        <v>17339</v>
       </c>
       <c r="H66" s="22" t="n">
-        <v>17455</v>
+        <v>17129</v>
       </c>
       <c r="I66" s="21" t="n">
-        <v>18007</v>
+        <v>18277</v>
       </c>
       <c r="J66" s="22" t="n">
-        <v>17728</v>
+        <v>17847</v>
       </c>
     </row>
     <row r="67">
@@ -5844,25 +5844,25 @@
         <v>17</v>
       </c>
       <c r="D67" s="21" t="n">
-        <v>17559</v>
+        <v>17586</v>
       </c>
       <c r="E67" s="22" t="n">
         <v>15659</v>
       </c>
       <c r="F67" s="21" t="n">
-        <v>17379</v>
+        <v>17556</v>
       </c>
       <c r="G67" s="21" t="n">
-        <v>17908</v>
+        <v>17846</v>
       </c>
       <c r="H67" s="22" t="n">
-        <v>17985</v>
+        <v>17646</v>
       </c>
       <c r="I67" s="21" t="n">
-        <v>18465</v>
+        <v>18599</v>
       </c>
       <c r="J67" s="22" t="n">
-        <v>18510</v>
+        <v>18740</v>
       </c>
     </row>
     <row r="68">
@@ -5876,25 +5876,25 @@
         <v>17</v>
       </c>
       <c r="D68" s="21" t="n">
-        <v>17737</v>
+        <v>17777</v>
       </c>
       <c r="E68" s="22" t="n">
-        <v>16126</v>
+        <v>16125</v>
       </c>
       <c r="F68" s="21" t="n">
-        <v>17481</v>
+        <v>17717</v>
       </c>
       <c r="G68" s="21" t="n">
-        <v>17769</v>
+        <v>17751</v>
       </c>
       <c r="H68" s="22" t="n">
-        <v>18254</v>
+        <v>17947</v>
       </c>
       <c r="I68" s="21" t="n">
-        <v>18767</v>
+        <v>18789</v>
       </c>
       <c r="J68" s="22" t="n">
-        <v>18524</v>
+        <v>18812</v>
       </c>
     </row>
     <row r="69">
@@ -5908,25 +5908,25 @@
         <v>17</v>
       </c>
       <c r="D69" s="21" t="n">
-        <v>17870</v>
+        <v>17982</v>
       </c>
       <c r="E69" s="22" t="n">
-        <v>16501</v>
+        <v>16498</v>
       </c>
       <c r="F69" s="21" t="n">
-        <v>17382</v>
+        <v>17956</v>
       </c>
       <c r="G69" s="21" t="n">
-        <v>18066</v>
+        <v>18012</v>
       </c>
       <c r="H69" s="22" t="n">
-        <v>18645</v>
+        <v>18335</v>
       </c>
       <c r="I69" s="21" t="n">
-        <v>18693</v>
+        <v>18714</v>
       </c>
       <c r="J69" s="22" t="n">
-        <v>18390</v>
+        <v>18815</v>
       </c>
     </row>
     <row r="70">
@@ -5940,25 +5940,25 @@
         <v>18</v>
       </c>
       <c r="D70" s="21" t="n">
-        <v>17917</v>
+        <v>17990</v>
       </c>
       <c r="E70" s="22" t="n">
-        <v>16817</v>
+        <v>16810</v>
       </c>
       <c r="F70" s="21" t="n">
-        <v>17485</v>
+        <v>17988</v>
       </c>
       <c r="G70" s="21" t="n">
-        <v>18046</v>
+        <v>18023</v>
       </c>
       <c r="H70" s="22" t="n">
-        <v>18690</v>
+        <v>18401</v>
       </c>
       <c r="I70" s="21" t="n">
-        <v>18437</v>
+        <v>18454</v>
       </c>
       <c r="J70" s="22" t="n">
-        <v>18411</v>
+        <v>18623</v>
       </c>
     </row>
     <row r="71">
@@ -5972,25 +5972,25 @@
         <v>18</v>
       </c>
       <c r="D71" s="21" t="n">
-        <v>18090</v>
+        <v>18183</v>
       </c>
       <c r="E71" s="22" t="n">
-        <v>17058</v>
+        <v>17052</v>
       </c>
       <c r="F71" s="21" t="n">
-        <v>17740</v>
+        <v>18151</v>
       </c>
       <c r="G71" s="21" t="n">
-        <v>18197</v>
+        <v>18136</v>
       </c>
       <c r="H71" s="22" t="n">
-        <v>18809</v>
+        <v>18607</v>
       </c>
       <c r="I71" s="21" t="n">
-        <v>18623</v>
+        <v>18669</v>
       </c>
       <c r="J71" s="22" t="n">
-        <v>18472</v>
+        <v>18835</v>
       </c>
     </row>
     <row r="72">
@@ -6004,25 +6004,25 @@
         <v>18</v>
       </c>
       <c r="D72" s="21" t="n">
-        <v>18145</v>
+        <v>18190</v>
       </c>
       <c r="E72" s="22" t="n">
-        <v>17264</v>
+        <v>17256</v>
       </c>
       <c r="F72" s="21" t="n">
-        <v>17790</v>
+        <v>18102</v>
       </c>
       <c r="G72" s="21" t="n">
-        <v>18191</v>
+        <v>18131</v>
       </c>
       <c r="H72" s="22" t="n">
-        <v>18813</v>
+        <v>18585</v>
       </c>
       <c r="I72" s="21" t="n">
-        <v>18562</v>
+        <v>18617</v>
       </c>
       <c r="J72" s="22" t="n">
-        <v>18565</v>
+        <v>18746</v>
       </c>
     </row>
     <row r="73">
@@ -6036,25 +6036,25 @@
         <v>18</v>
       </c>
       <c r="D73" s="21" t="n">
-        <v>18502</v>
+        <v>18600</v>
       </c>
       <c r="E73" s="22" t="n">
-        <v>17394</v>
+        <v>17385</v>
       </c>
       <c r="F73" s="21" t="n">
-        <v>18225</v>
+        <v>18613</v>
       </c>
       <c r="G73" s="21" t="n">
-        <v>18779</v>
+        <v>18790</v>
       </c>
       <c r="H73" s="22" t="n">
-        <v>18977</v>
+        <v>18800</v>
       </c>
       <c r="I73" s="21" t="n">
-        <v>18859</v>
+        <v>18941</v>
       </c>
       <c r="J73" s="22" t="n">
-        <v>19120</v>
+        <v>19415</v>
       </c>
     </row>
     <row r="74">
@@ -6068,25 +6068,25 @@
         <v>19</v>
       </c>
       <c r="D74" s="21" t="n">
-        <v>18417</v>
+        <v>18484</v>
       </c>
       <c r="E74" s="22" t="n">
-        <v>17466</v>
+        <v>17455</v>
       </c>
       <c r="F74" s="21" t="n">
-        <v>18695</v>
+        <v>18725</v>
       </c>
       <c r="G74" s="21" t="n">
-        <v>18243</v>
+        <v>18444</v>
       </c>
       <c r="H74" s="22" t="n">
-        <v>18881</v>
+        <v>18715</v>
       </c>
       <c r="I74" s="21" t="n">
-        <v>18573</v>
+        <v>18709</v>
       </c>
       <c r="J74" s="22" t="n">
-        <v>18934</v>
+        <v>19149</v>
       </c>
     </row>
     <row r="75">
@@ -6100,25 +6100,25 @@
         <v>19</v>
       </c>
       <c r="D75" s="21" t="n">
-        <v>18246</v>
+        <v>18294</v>
       </c>
       <c r="E75" s="22" t="n">
-        <v>17235</v>
+        <v>17223</v>
       </c>
       <c r="F75" s="21" t="n">
+        <v>18419</v>
+      </c>
+      <c r="G75" s="21" t="n">
         <v>18555</v>
       </c>
-      <c r="G75" s="21" t="n">
-        <v>18244</v>
-      </c>
       <c r="H75" s="22" t="n">
-        <v>18627</v>
+        <v>18448</v>
       </c>
       <c r="I75" s="21" t="n">
-        <v>18443</v>
+        <v>18594</v>
       </c>
       <c r="J75" s="22" t="n">
-        <v>18663</v>
+        <v>18818</v>
       </c>
     </row>
     <row r="76">
@@ -6132,25 +6132,25 @@
         <v>19</v>
       </c>
       <c r="D76" s="21" t="n">
-        <v>17935</v>
+        <v>17990</v>
       </c>
       <c r="E76" s="22" t="n">
-        <v>16947</v>
+        <v>16933</v>
       </c>
       <c r="F76" s="21" t="n">
-        <v>18052</v>
+        <v>18111</v>
       </c>
       <c r="G76" s="21" t="n">
-        <v>17836</v>
+        <v>18216</v>
       </c>
       <c r="H76" s="22" t="n">
-        <v>18392</v>
+        <v>18171</v>
       </c>
       <c r="I76" s="21" t="n">
-        <v>18261</v>
+        <v>18299</v>
       </c>
       <c r="J76" s="22" t="n">
-        <v>18428</v>
+        <v>18501</v>
       </c>
     </row>
     <row r="77">
@@ -6164,25 +6164,25 @@
         <v>19</v>
       </c>
       <c r="D77" s="21" t="n">
-        <v>17502</v>
+        <v>17469</v>
       </c>
       <c r="E77" s="22" t="n">
-        <v>16613</v>
+        <v>16600</v>
       </c>
       <c r="F77" s="21" t="n">
-        <v>17510</v>
+        <v>17313</v>
       </c>
       <c r="G77" s="21" t="n">
-        <v>17609</v>
+        <v>17703</v>
       </c>
       <c r="H77" s="22" t="n">
-        <v>18036</v>
+        <v>17826</v>
       </c>
       <c r="I77" s="21" t="n">
-        <v>17685</v>
+        <v>17753</v>
       </c>
       <c r="J77" s="22" t="n">
-        <v>17838</v>
+        <v>17884</v>
       </c>
     </row>
     <row r="78">
@@ -6196,25 +6196,25 @@
         <v>20</v>
       </c>
       <c r="D78" s="21" t="n">
-        <v>16979</v>
+        <v>17040</v>
       </c>
       <c r="E78" s="22" t="n">
-        <v>16414</v>
+        <v>16400</v>
       </c>
       <c r="F78" s="21" t="n">
-        <v>17015</v>
+        <v>17161</v>
       </c>
       <c r="G78" s="21" t="n">
-        <v>16790</v>
+        <v>16978</v>
       </c>
       <c r="H78" s="22" t="n">
-        <v>17598</v>
+        <v>17367</v>
       </c>
       <c r="I78" s="21" t="n">
-        <v>17045</v>
+        <v>17188</v>
       </c>
       <c r="J78" s="22" t="n">
-        <v>17220</v>
+        <v>17347</v>
       </c>
     </row>
     <row r="79">
@@ -6228,25 +6228,25 @@
         <v>20</v>
       </c>
       <c r="D79" s="21" t="n">
-        <v>16749</v>
+        <v>16772</v>
       </c>
       <c r="E79" s="22" t="n">
-        <v>16285</v>
+        <v>16271</v>
       </c>
       <c r="F79" s="21" t="n">
-        <v>16777</v>
+        <v>17027</v>
       </c>
       <c r="G79" s="21" t="n">
-        <v>16542</v>
+        <v>16416</v>
       </c>
       <c r="H79" s="22" t="n">
-        <v>17329</v>
+        <v>17119</v>
       </c>
       <c r="I79" s="21" t="n">
-        <v>16869</v>
+        <v>17054</v>
       </c>
       <c r="J79" s="22" t="n">
-        <v>16873</v>
+        <v>16922</v>
       </c>
     </row>
     <row r="80">
@@ -6260,25 +6260,25 @@
         <v>20</v>
       </c>
       <c r="D80" s="21" t="n">
-        <v>16607</v>
+        <v>16649</v>
       </c>
       <c r="E80" s="22" t="n">
-        <v>16148</v>
+        <v>16133</v>
       </c>
       <c r="F80" s="21" t="n">
-        <v>16580</v>
+        <v>16915</v>
       </c>
       <c r="G80" s="21" t="n">
-        <v>16355</v>
+        <v>16342</v>
       </c>
       <c r="H80" s="22" t="n">
-        <v>17128</v>
+        <v>16903</v>
       </c>
       <c r="I80" s="21" t="n">
-        <v>16789</v>
+        <v>16893</v>
       </c>
       <c r="J80" s="22" t="n">
-        <v>16821</v>
+        <v>16876</v>
       </c>
     </row>
     <row r="81">
@@ -6292,25 +6292,25 @@
         <v>20</v>
       </c>
       <c r="D81" s="21" t="n">
-        <v>16445</v>
+        <v>16470</v>
       </c>
       <c r="E81" s="22" t="n">
-        <v>16001</v>
+        <v>15986</v>
       </c>
       <c r="F81" s="21" t="n">
-        <v>16437</v>
+        <v>16730</v>
       </c>
       <c r="G81" s="21" t="n">
-        <v>16281</v>
+        <v>16268</v>
       </c>
       <c r="H81" s="22" t="n">
-        <v>16913</v>
+        <v>16715</v>
       </c>
       <c r="I81" s="21" t="n">
-        <v>16635</v>
+        <v>16678</v>
       </c>
       <c r="J81" s="22" t="n">
-        <v>16568</v>
+        <v>16600</v>
       </c>
     </row>
     <row r="82">
@@ -6324,25 +6324,25 @@
         <v>21</v>
       </c>
       <c r="D82" s="21" t="n">
-        <v>16439</v>
+        <v>16440</v>
       </c>
       <c r="E82" s="22" t="n">
-        <v>15961</v>
+        <v>15945</v>
       </c>
       <c r="F82" s="21" t="n">
-        <v>16482</v>
+        <v>16655</v>
       </c>
       <c r="G82" s="21" t="n">
-        <v>16260</v>
+        <v>16247</v>
       </c>
       <c r="H82" s="22" t="n">
-        <v>16869</v>
+        <v>16680</v>
       </c>
       <c r="I82" s="21" t="n">
-        <v>16672</v>
+        <v>16676</v>
       </c>
       <c r="J82" s="22" t="n">
-        <v>16560</v>
+        <v>16597</v>
       </c>
     </row>
     <row r="83">
@@ -6356,25 +6356,25 @@
         <v>21</v>
       </c>
       <c r="D83" s="21" t="n">
-        <v>16506</v>
+        <v>16519</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>15950</v>
+        <v>15935</v>
       </c>
       <c r="F83" s="21" t="n">
-        <v>16576</v>
+        <v>16991</v>
       </c>
       <c r="G83" s="21" t="n">
-        <v>16271</v>
+        <v>16257</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>16924</v>
+        <v>16705</v>
       </c>
       <c r="I83" s="21" t="n">
-        <v>16830</v>
+        <v>16773</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>16679</v>
+        <v>16622</v>
       </c>
     </row>
     <row r="84">
@@ -6388,25 +6388,25 @@
         <v>21</v>
       </c>
       <c r="D84" s="21" t="n">
-        <v>16637</v>
+        <v>16684</v>
       </c>
       <c r="E84" s="22" t="n">
-        <v>15973</v>
+        <v>15959</v>
       </c>
       <c r="F84" s="21" t="n">
-        <v>16698</v>
+        <v>17057</v>
       </c>
       <c r="G84" s="21" t="n">
-        <v>16345</v>
+        <v>16331</v>
       </c>
       <c r="H84" s="22" t="n">
-        <v>17104</v>
+        <v>16906</v>
       </c>
       <c r="I84" s="21" t="n">
-        <v>16993</v>
+        <v>17061</v>
       </c>
       <c r="J84" s="22" t="n">
-        <v>16943</v>
+        <v>17014</v>
       </c>
     </row>
     <row r="85">
@@ -6420,25 +6420,25 @@
         <v>21</v>
       </c>
       <c r="D85" s="21" t="n">
-        <v>16792</v>
+        <v>16787</v>
       </c>
       <c r="E85" s="22" t="n">
-        <v>16005</v>
+        <v>15992</v>
       </c>
       <c r="F85" s="21" t="n">
-        <v>16964</v>
+        <v>17051</v>
       </c>
       <c r="G85" s="21" t="n">
-        <v>16472</v>
+        <v>16376</v>
       </c>
       <c r="H85" s="22" t="n">
-        <v>17308</v>
+        <v>17120</v>
       </c>
       <c r="I85" s="21" t="n">
-        <v>17112</v>
+        <v>17238</v>
       </c>
       <c r="J85" s="22" t="n">
-        <v>17152</v>
+        <v>17205</v>
       </c>
     </row>
     <row r="86">
@@ -6452,25 +6452,25 @@
         <v>22</v>
       </c>
       <c r="D86" s="21" t="n">
-        <v>16950</v>
+        <v>16915</v>
       </c>
       <c r="E86" s="22" t="n">
-        <v>16073</v>
+        <v>16061</v>
       </c>
       <c r="F86" s="21" t="n">
-        <v>17345</v>
+        <v>17255</v>
       </c>
       <c r="G86" s="21" t="n">
-        <v>16584</v>
+        <v>16455</v>
       </c>
       <c r="H86" s="22" t="n">
-        <v>17467</v>
+        <v>17310</v>
       </c>
       <c r="I86" s="21" t="n">
-        <v>17300</v>
+        <v>17415</v>
       </c>
       <c r="J86" s="22" t="n">
-        <v>17210</v>
+        <v>17275</v>
       </c>
     </row>
     <row r="87">
@@ -6484,25 +6484,25 @@
         <v>22</v>
       </c>
       <c r="D87" s="21" t="n">
-        <v>16772</v>
+        <v>16769</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>15981</v>
+        <v>15968</v>
       </c>
       <c r="F87" s="21" t="n">
-        <v>17044</v>
+        <v>17109</v>
       </c>
       <c r="G87" s="21" t="n">
-        <v>16355</v>
+        <v>16342</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>17266</v>
+        <v>17086</v>
       </c>
       <c r="I87" s="21" t="n">
-        <v>17124</v>
+        <v>17182</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>17126</v>
+        <v>17182</v>
       </c>
     </row>
     <row r="88">
@@ -6516,25 +6516,25 @@
         <v>22</v>
       </c>
       <c r="D88" s="21" t="n">
-        <v>16632</v>
+        <v>16606</v>
       </c>
       <c r="E88" s="22" t="n">
-        <v>15823</v>
+        <v>15808</v>
       </c>
       <c r="F88" s="21" t="n">
-        <v>16925</v>
+        <v>17024</v>
       </c>
       <c r="G88" s="21" t="n">
-        <v>16281</v>
+        <v>16218</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>17086</v>
+        <v>16879</v>
       </c>
       <c r="I88" s="21" t="n">
-        <v>17049</v>
+        <v>17003</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>16889</v>
+        <v>16951</v>
       </c>
     </row>
     <row r="89">
@@ -6548,25 +6548,25 @@
         <v>22</v>
       </c>
       <c r="D89" s="21" t="n">
-        <v>16374</v>
+        <v>16424</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>15624</v>
+        <v>15608</v>
       </c>
       <c r="F89" s="21" t="n">
-        <v>16662</v>
+        <v>16974</v>
       </c>
       <c r="G89" s="21" t="n">
-        <v>16164</v>
+        <v>16101</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>16763</v>
+        <v>16613</v>
       </c>
       <c r="I89" s="21" t="n">
-        <v>16622</v>
+        <v>16744</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>16641</v>
+        <v>16739</v>
       </c>
     </row>
     <row r="90">
@@ -6580,25 +6580,25 @@
         <v>23</v>
       </c>
       <c r="D90" s="21" t="n">
-        <v>16321</v>
+        <v>16349</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>15526</v>
+        <v>15509</v>
       </c>
       <c r="F90" s="21" t="n">
-        <v>16700</v>
+        <v>16931</v>
       </c>
       <c r="G90" s="21" t="n">
-        <v>16147</v>
+        <v>16085</v>
       </c>
       <c r="H90" s="22" t="n">
-        <v>16638</v>
+        <v>16465</v>
       </c>
       <c r="I90" s="21" t="n">
-        <v>16600</v>
+        <v>16706</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>16543</v>
+        <v>16630</v>
       </c>
     </row>
     <row r="91">
@@ -6612,25 +6612,25 @@
         <v>23</v>
       </c>
       <c r="D91" s="21" t="n">
-        <v>16286</v>
+        <v>16327</v>
       </c>
       <c r="E91" s="22" t="n">
-        <v>15426</v>
+        <v>15410</v>
       </c>
       <c r="F91" s="21" t="n">
-        <v>16588</v>
+        <v>16783</v>
       </c>
       <c r="G91" s="21" t="n">
-        <v>16152</v>
+        <v>16088</v>
       </c>
       <c r="H91" s="22" t="n">
-        <v>16552</v>
+        <v>16500</v>
       </c>
       <c r="I91" s="21" t="n">
-        <v>16636</v>
+        <v>16785</v>
       </c>
       <c r="J91" s="22" t="n">
-        <v>16612</v>
+        <v>16660</v>
       </c>
     </row>
     <row r="92">
@@ -6644,25 +6644,25 @@
         <v>23</v>
       </c>
       <c r="D92" s="21" t="n">
-        <v>16280</v>
+        <v>16315</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>15368</v>
+        <v>15353</v>
       </c>
       <c r="F92" s="21" t="n">
-        <v>16608</v>
+        <v>16779</v>
       </c>
       <c r="G92" s="21" t="n">
-        <v>16114</v>
+        <v>16051</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>16617</v>
+        <v>16570</v>
       </c>
       <c r="I92" s="21" t="n">
-        <v>16644</v>
+        <v>16771</v>
       </c>
       <c r="J92" s="22" t="n">
-        <v>16598</v>
+        <v>16650</v>
       </c>
     </row>
     <row r="93">
@@ -6676,25 +6676,25 @@
         <v>23</v>
       </c>
       <c r="D93" s="21" t="n">
-        <v>16255</v>
+        <v>16298</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>15282</v>
+        <v>15268</v>
       </c>
       <c r="F93" s="21" t="n">
-        <v>16647</v>
+        <v>16814</v>
       </c>
       <c r="G93" s="21" t="n">
-        <v>16084</v>
+        <v>16036</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>16605</v>
+        <v>16530</v>
       </c>
       <c r="I93" s="21" t="n">
-        <v>16595</v>
+        <v>16761</v>
       </c>
       <c r="J93" s="22" t="n">
-        <v>16600</v>
+        <v>16678</v>
       </c>
     </row>
     <row r="94">
@@ -6708,25 +6708,25 @@
         <v>24</v>
       </c>
       <c r="D94" s="21" t="n">
-        <v>16278</v>
+        <v>16304</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>15284</v>
+        <v>15269</v>
       </c>
       <c r="F94" s="21" t="n">
-        <v>16581</v>
+        <v>16731</v>
       </c>
       <c r="G94" s="21" t="n">
-        <v>16101</v>
+        <v>16036</v>
       </c>
       <c r="H94" s="22" t="n">
-        <v>16708</v>
+        <v>16679</v>
       </c>
       <c r="I94" s="21" t="n">
-        <v>16596</v>
+        <v>16695</v>
       </c>
       <c r="J94" s="22" t="n">
-        <v>16699</v>
+        <v>16729</v>
       </c>
     </row>
     <row r="95">
@@ -6740,25 +6740,25 @@
         <v>24</v>
       </c>
       <c r="D95" s="21" t="n">
-        <v>16024</v>
+        <v>16067</v>
       </c>
       <c r="E95" s="22" t="n">
-        <v>15161</v>
+        <v>15146</v>
       </c>
       <c r="F95" s="21" t="n">
-        <v>16175</v>
+        <v>16347</v>
       </c>
       <c r="G95" s="21" t="n">
-        <v>15846</v>
+        <v>15893</v>
       </c>
       <c r="H95" s="22" t="n">
-        <v>16408</v>
+        <v>16360</v>
       </c>
       <c r="I95" s="21" t="n">
-        <v>16323</v>
+        <v>16405</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>16498</v>
+        <v>16530</v>
       </c>
     </row>
     <row r="96">
@@ -6772,25 +6772,25 @@
         <v>24</v>
       </c>
       <c r="D96" s="21" t="n">
-        <v>16023</v>
+        <v>16073</v>
       </c>
       <c r="E96" s="22" t="n">
-        <v>15116</v>
+        <v>15102</v>
       </c>
       <c r="F96" s="21" t="n">
-        <v>16199</v>
+        <v>16307</v>
       </c>
       <c r="G96" s="21" t="n">
-        <v>15901</v>
+        <v>15948</v>
       </c>
       <c r="H96" s="22" t="n">
-        <v>16496</v>
+        <v>16448</v>
       </c>
       <c r="I96" s="21" t="n">
-        <v>16267</v>
+        <v>16422</v>
       </c>
       <c r="J96" s="22" t="n">
-        <v>16443</v>
+        <v>16512</v>
       </c>
     </row>
     <row r="97">
@@ -6806,25 +6806,25 @@
         <v>24</v>
       </c>
       <c r="D97" s="21" t="n">
-        <v>16009</v>
+        <v>16052</v>
       </c>
       <c r="E97" s="22" t="n">
-        <v>15087</v>
+        <v>15073</v>
       </c>
       <c r="F97" s="21" t="n">
-        <v>16040</v>
+        <v>16180</v>
       </c>
       <c r="G97" s="21" t="n">
-        <v>16059</v>
+        <v>16006</v>
       </c>
       <c r="H97" s="22" t="n">
-        <v>16502</v>
+        <v>16418</v>
       </c>
       <c r="I97" s="21" t="n">
-        <v>16227</v>
+        <v>16420</v>
       </c>
       <c r="J97" s="22" t="n">
-        <v>16427</v>
+        <v>16517</v>
       </c>
     </row>
   </sheetData>
@@ -6989,25 +6989,25 @@
         <v>379</v>
       </c>
       <c r="G2" s="23" t="n">
-        <v>330.57</v>
+        <v>327.57</v>
       </c>
       <c r="H2" s="24" t="n">
-        <v>282.5</v>
+        <v>282.11</v>
       </c>
       <c r="I2" s="23" t="n">
-        <v>337.77</v>
+        <v>343.33</v>
       </c>
       <c r="J2" s="23" t="n">
-        <v>355.31</v>
+        <v>333.71</v>
       </c>
       <c r="K2" s="24" t="n">
-        <v>375.78</v>
+        <v>376.29</v>
       </c>
       <c r="L2" s="23" t="n">
-        <v>311.66</v>
+        <v>309.29</v>
       </c>
       <c r="M2" s="24" t="n">
-        <v>316.71</v>
+        <v>317.13</v>
       </c>
     </row>
     <row r="3">
@@ -7030,25 +7030,25 @@
         <v>379</v>
       </c>
       <c r="G3" s="23" t="n">
-        <v>322.03</v>
+        <v>319.78</v>
       </c>
       <c r="H3" s="24" t="n">
-        <v>273.51</v>
+        <v>273.16</v>
       </c>
       <c r="I3" s="23" t="n">
-        <v>328.49</v>
+        <v>323.32</v>
       </c>
       <c r="J3" s="23" t="n">
-        <v>346.73</v>
+        <v>340.08</v>
       </c>
       <c r="K3" s="24" t="n">
-        <v>359.2</v>
+        <v>363.57</v>
       </c>
       <c r="L3" s="23" t="n">
-        <v>309.48</v>
+        <v>306.67</v>
       </c>
       <c r="M3" s="24" t="n">
-        <v>311.01</v>
+        <v>308.8</v>
       </c>
     </row>
     <row r="4">
@@ -7071,25 +7071,25 @@
         <v>379</v>
       </c>
       <c r="G4" s="23" t="n">
-        <v>319.86</v>
+        <v>318.19</v>
       </c>
       <c r="H4" s="24" t="n">
-        <v>272</v>
+        <v>271.72</v>
       </c>
       <c r="I4" s="23" t="n">
-        <v>331.91</v>
+        <v>322.71</v>
       </c>
       <c r="J4" s="23" t="n">
-        <v>339.67</v>
+        <v>338.63</v>
       </c>
       <c r="K4" s="24" t="n">
-        <v>352.62</v>
+        <v>356.23</v>
       </c>
       <c r="L4" s="23" t="n">
-        <v>308.76</v>
+        <v>308.51</v>
       </c>
       <c r="M4" s="24" t="n">
-        <v>310.19</v>
+        <v>308.21</v>
       </c>
     </row>
     <row r="5">
@@ -7112,25 +7112,25 @@
         <v>379</v>
       </c>
       <c r="G5" s="23" t="n">
-        <v>318.55</v>
+        <v>312.82</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>266.48</v>
+        <v>266.17</v>
       </c>
       <c r="I5" s="23" t="n">
-        <v>327.76</v>
+        <v>312.84</v>
       </c>
       <c r="J5" s="23" t="n">
-        <v>331.97</v>
+        <v>325.1</v>
       </c>
       <c r="K5" s="24" t="n">
-        <v>348.81</v>
+        <v>347.03</v>
       </c>
       <c r="L5" s="23" t="n">
-        <v>316.58</v>
+        <v>310.39</v>
       </c>
       <c r="M5" s="24" t="n">
-        <v>315.07</v>
+        <v>311.93</v>
       </c>
     </row>
     <row r="6">
@@ -7153,25 +7153,25 @@
         <v>379</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>311.96</v>
+        <v>305.02</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>258.37</v>
+        <v>257.99</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>314.08</v>
+        <v>320.66</v>
       </c>
       <c r="J6" s="23" t="n">
-        <v>327.8</v>
+        <v>312.31</v>
       </c>
       <c r="K6" s="24" t="n">
-        <v>339.05</v>
+        <v>332.08</v>
       </c>
       <c r="L6" s="23" t="n">
-        <v>320.45</v>
+        <v>304.67</v>
       </c>
       <c r="M6" s="24" t="n">
-        <v>307.46</v>
+        <v>298.52</v>
       </c>
     </row>
     <row r="7">
@@ -7194,25 +7194,25 @@
         <v>379</v>
       </c>
       <c r="G7" s="23" t="n">
-        <v>308.71</v>
+        <v>302.76</v>
       </c>
       <c r="H7" s="24" t="n">
-        <v>255.33</v>
+        <v>254.95</v>
       </c>
       <c r="I7" s="23" t="n">
-        <v>311.14</v>
+        <v>320.97</v>
       </c>
       <c r="J7" s="23" t="n">
-        <v>325.03</v>
+        <v>311.83</v>
       </c>
       <c r="K7" s="24" t="n">
-        <v>337.01</v>
+        <v>319.44</v>
       </c>
       <c r="L7" s="23" t="n">
-        <v>317.99</v>
+        <v>309.54</v>
       </c>
       <c r="M7" s="24" t="n">
-        <v>301.28</v>
+        <v>295.83</v>
       </c>
     </row>
     <row r="8">
@@ -7235,25 +7235,25 @@
         <v>379</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>302.94</v>
+        <v>293.53</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>247.72</v>
+        <v>247.33</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>300.64</v>
+        <v>310.34</v>
       </c>
       <c r="J8" s="23" t="n">
-        <v>325.05</v>
+        <v>300.35</v>
       </c>
       <c r="K8" s="24" t="n">
-        <v>335.24</v>
+        <v>314.8</v>
       </c>
       <c r="L8" s="23" t="n">
-        <v>300.21</v>
+        <v>284.99</v>
       </c>
       <c r="M8" s="24" t="n">
-        <v>304.4</v>
+        <v>299.53</v>
       </c>
     </row>
     <row r="9">
@@ -7276,25 +7276,25 @@
         <v>379</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>316.47</v>
+        <v>310.18</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>266.21</v>
+        <v>265.92</v>
       </c>
       <c r="I9" s="23" t="n">
-        <v>323.53</v>
+        <v>319.7</v>
       </c>
       <c r="J9" s="23" t="n">
-        <v>326.93</v>
+        <v>324.29</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>341.22</v>
+        <v>332.28</v>
       </c>
       <c r="L9" s="23" t="n">
-        <v>332.3</v>
+        <v>320.94</v>
       </c>
       <c r="M9" s="24" t="n">
-        <v>304.07</v>
+        <v>294.58</v>
       </c>
     </row>
     <row r="10">
@@ -7317,25 +7317,25 @@
         <v>385</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>353.18</v>
+        <v>354.21</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>319.98</v>
+        <v>319.73</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>349.9</v>
+        <v>362.4</v>
       </c>
       <c r="J10" s="23" t="n">
-        <v>383.78</v>
+        <v>372.07</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>372.26</v>
+        <v>364.79</v>
       </c>
       <c r="L10" s="23" t="n">
-        <v>361.03</v>
+        <v>358.05</v>
       </c>
       <c r="M10" s="24" t="n">
-        <v>330.12</v>
+        <v>345.81</v>
       </c>
     </row>
     <row r="11">
@@ -7358,25 +7358,25 @@
         <v>385</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>360.1</v>
+        <v>355.78</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>306.99</v>
+        <v>306.55</v>
       </c>
       <c r="I11" s="23" t="n">
-        <v>357.65</v>
+        <v>358.52</v>
       </c>
       <c r="J11" s="23" t="n">
-        <v>383.09</v>
+        <v>370.32</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>370.28</v>
+        <v>365.05</v>
       </c>
       <c r="L11" s="23" t="n">
-        <v>373.68</v>
+        <v>365.44</v>
       </c>
       <c r="M11" s="24" t="n">
-        <v>364.61</v>
+        <v>364.91</v>
       </c>
     </row>
     <row r="12">
@@ -7399,25 +7399,25 @@
         <v>385</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>348.11</v>
+        <v>345.62</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>294.77</v>
+        <v>294.29</v>
       </c>
       <c r="I12" s="23" t="n">
-        <v>338.99</v>
+        <v>355.36</v>
       </c>
       <c r="J12" s="23" t="n">
-        <v>373.37</v>
+        <v>362.85</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>370.17</v>
+        <v>364.23</v>
       </c>
       <c r="L12" s="23" t="n">
-        <v>354.68</v>
+        <v>343.95</v>
       </c>
       <c r="M12" s="24" t="n">
-        <v>352.68</v>
+        <v>349.15</v>
       </c>
     </row>
     <row r="13">
@@ -7440,25 +7440,25 @@
         <v>385</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>334.72</v>
+        <v>327.7</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>281.81</v>
+        <v>281.34</v>
       </c>
       <c r="I13" s="23" t="n">
-        <v>341.94</v>
+        <v>332.44</v>
       </c>
       <c r="J13" s="23" t="n">
-        <v>358.19</v>
+        <v>353.58</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>359.74</v>
+        <v>357.22</v>
       </c>
       <c r="L13" s="23" t="n">
-        <v>334.79</v>
+        <v>316.79</v>
       </c>
       <c r="M13" s="24" t="n">
-        <v>327.49</v>
+        <v>321.87</v>
       </c>
     </row>
     <row r="14">
@@ -7481,25 +7481,25 @@
         <v>380</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>330.29</v>
+        <v>323.5</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>274.25</v>
+        <v>273.77</v>
       </c>
       <c r="I14" s="23" t="n">
-        <v>340.32</v>
+        <v>330.22</v>
       </c>
       <c r="J14" s="23" t="n">
-        <v>352.95</v>
+        <v>345.07</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>348.48</v>
+        <v>349.71</v>
       </c>
       <c r="L14" s="23" t="n">
-        <v>332.88</v>
+        <v>319.46</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>328.09</v>
+        <v>319.29</v>
       </c>
     </row>
     <row r="15">
@@ -7522,25 +7522,25 @@
         <v>380</v>
       </c>
       <c r="G15" s="23" t="n">
-        <v>330.76</v>
+        <v>325.09</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>276.98</v>
+        <v>276.55</v>
       </c>
       <c r="I15" s="23" t="n">
-        <v>340.22</v>
+        <v>337.68</v>
       </c>
       <c r="J15" s="23" t="n">
-        <v>352.95</v>
+        <v>345.07</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>347.98</v>
+        <v>349.02</v>
       </c>
       <c r="L15" s="23" t="n">
-        <v>335.87</v>
+        <v>319.39</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>326</v>
+        <v>319.33</v>
       </c>
     </row>
     <row r="16">
@@ -7563,25 +7563,25 @@
         <v>380</v>
       </c>
       <c r="G16" s="23" t="n">
-        <v>330.51</v>
+        <v>325.56</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>277.22</v>
+        <v>276.81</v>
       </c>
       <c r="I16" s="23" t="n">
-        <v>338.07</v>
+        <v>337.88</v>
       </c>
       <c r="J16" s="23" t="n">
-        <v>354.77</v>
+        <v>347.5</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>347.96</v>
+        <v>348.23</v>
       </c>
       <c r="L16" s="23" t="n">
-        <v>335.35</v>
+        <v>317.28</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>325.25</v>
+        <v>322.23</v>
       </c>
     </row>
     <row r="17">
@@ -7604,25 +7604,25 @@
         <v>380</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>328.65</v>
+        <v>324.38</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>273.68</v>
+        <v>273.26</v>
       </c>
       <c r="I17" s="23" t="n">
-        <v>337.11</v>
+        <v>333.22</v>
       </c>
       <c r="J17" s="23" t="n">
-        <v>351.43</v>
+        <v>346.9</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>347.52</v>
+        <v>347.24</v>
       </c>
       <c r="L17" s="23" t="n">
-        <v>333.25</v>
+        <v>321.08</v>
       </c>
       <c r="M17" s="24" t="n">
-        <v>324.3</v>
+        <v>320.96</v>
       </c>
     </row>
     <row r="18">
@@ -7645,25 +7645,25 @@
         <v>380</v>
       </c>
       <c r="G18" s="23" t="n">
-        <v>328.51</v>
+        <v>323.2</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>273.99</v>
+        <v>273.56</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>331.06</v>
+        <v>326.94</v>
       </c>
       <c r="J18" s="23" t="n">
-        <v>352.67</v>
+        <v>346.9</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>347.29</v>
+        <v>346.41</v>
       </c>
       <c r="L18" s="23" t="n">
-        <v>336.98</v>
+        <v>319.6</v>
       </c>
       <c r="M18" s="24" t="n">
-        <v>324.63</v>
+        <v>322.38</v>
       </c>
     </row>
     <row r="19">
@@ -7686,25 +7686,25 @@
         <v>380</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>331.49</v>
+        <v>325.07</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>276.87</v>
+        <v>276.46</v>
       </c>
       <c r="I19" s="23" t="n">
-        <v>336.69</v>
+        <v>329.02</v>
       </c>
       <c r="J19" s="23" t="n">
-        <v>356.41</v>
+        <v>348.32</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>347.98</v>
+        <v>346.66</v>
       </c>
       <c r="L19" s="23" t="n">
-        <v>339.29</v>
+        <v>322.76</v>
       </c>
       <c r="M19" s="24" t="n">
-        <v>327.24</v>
+        <v>323.89</v>
       </c>
     </row>
     <row r="20">
@@ -7727,25 +7727,25 @@
         <v>380</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>331.4</v>
+        <v>325.15</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>278.49</v>
+        <v>278.09</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>333.74</v>
+        <v>330.79</v>
       </c>
       <c r="J20" s="23" t="n">
-        <v>356.41</v>
+        <v>348.32</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>352.35</v>
+        <v>348.3</v>
       </c>
       <c r="L20" s="23" t="n">
-        <v>338.14</v>
+        <v>319.84</v>
       </c>
       <c r="M20" s="24" t="n">
-        <v>325.07</v>
+        <v>322.41</v>
       </c>
     </row>
     <row r="21">
@@ -7768,25 +7768,25 @@
         <v>380</v>
       </c>
       <c r="G21" s="23" t="n">
-        <v>345.07</v>
+        <v>340.66</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>291.03</v>
+        <v>290.66</v>
       </c>
       <c r="I21" s="23" t="n">
-        <v>351.04</v>
+        <v>340.05</v>
       </c>
       <c r="J21" s="23" t="n">
-        <v>375</v>
+        <v>365.32</v>
       </c>
       <c r="K21" s="24" t="n">
-        <v>367.92</v>
+        <v>363.55</v>
       </c>
       <c r="L21" s="23" t="n">
-        <v>340.83</v>
+        <v>341.23</v>
       </c>
       <c r="M21" s="24" t="n">
-        <v>340.38</v>
+        <v>339.81</v>
       </c>
     </row>
     <row r="22">
@@ -7809,25 +7809,25 @@
         <v>398.99</v>
       </c>
       <c r="G22" s="23" t="n">
-        <v>360.28</v>
+        <v>357.62</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>304.15</v>
+        <v>303.73</v>
       </c>
       <c r="I22" s="23" t="n">
-        <v>364.39</v>
+        <v>361.15</v>
       </c>
       <c r="J22" s="23" t="n">
-        <v>385.04</v>
+        <v>373.67</v>
       </c>
       <c r="K22" s="24" t="n">
-        <v>378.34</v>
+        <v>370.64</v>
       </c>
       <c r="L22" s="23" t="n">
-        <v>366.3</v>
+        <v>369.27</v>
       </c>
       <c r="M22" s="24" t="n">
-        <v>358.85</v>
+        <v>363.07</v>
       </c>
     </row>
     <row r="23">
@@ -7850,25 +7850,25 @@
         <v>398.99</v>
       </c>
       <c r="G23" s="23" t="n">
-        <v>364.69</v>
+        <v>361.94</v>
       </c>
       <c r="H23" s="24" t="n">
-        <v>313.56</v>
+        <v>313.08</v>
       </c>
       <c r="I23" s="23" t="n">
-        <v>374.59</v>
+        <v>362.76</v>
       </c>
       <c r="J23" s="23" t="n">
-        <v>386.16</v>
+        <v>381.91</v>
       </c>
       <c r="K23" s="24" t="n">
-        <v>373.78</v>
+        <v>371.22</v>
       </c>
       <c r="L23" s="23" t="n">
-        <v>374.59</v>
+        <v>371.34</v>
       </c>
       <c r="M23" s="24" t="n">
-        <v>361.03</v>
+        <v>367.74</v>
       </c>
     </row>
     <row r="24">
@@ -7891,25 +7891,25 @@
         <v>398.99</v>
       </c>
       <c r="G24" s="23" t="n">
-        <v>370.53</v>
+        <v>369.65</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>324.64</v>
+        <v>324.18</v>
       </c>
       <c r="I24" s="23" t="n">
-        <v>380.55</v>
+        <v>379.14</v>
       </c>
       <c r="J24" s="23" t="n">
-        <v>390.79</v>
+        <v>384.67</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>374.66</v>
+        <v>374.91</v>
       </c>
       <c r="L24" s="23" t="n">
-        <v>382.03</v>
+        <v>375.13</v>
       </c>
       <c r="M24" s="24" t="n">
-        <v>366.56</v>
+        <v>376.31</v>
       </c>
     </row>
     <row r="25">
@@ -7932,25 +7932,25 @@
         <v>398.99</v>
       </c>
       <c r="G25" s="23" t="n">
-        <v>371.21</v>
+        <v>373.21</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>330.88</v>
+        <v>330.42</v>
       </c>
       <c r="I25" s="23" t="n">
-        <v>377.24</v>
+        <v>380.49</v>
       </c>
       <c r="J25" s="23" t="n">
-        <v>389.87</v>
+        <v>392.07</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>378.16</v>
+        <v>378.23</v>
       </c>
       <c r="L25" s="23" t="n">
-        <v>381.15</v>
+        <v>376.9</v>
       </c>
       <c r="M25" s="24" t="n">
-        <v>366.55</v>
+        <v>378.02</v>
       </c>
     </row>
     <row r="26">
@@ -7973,25 +7973,25 @@
         <v>400</v>
       </c>
       <c r="G26" s="23" t="n">
-        <v>378.62</v>
+        <v>380.83</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>342.2</v>
+        <v>341.77</v>
       </c>
       <c r="I26" s="23" t="n">
-        <v>383.28</v>
+        <v>384.48</v>
       </c>
       <c r="J26" s="23" t="n">
-        <v>392.59</v>
+        <v>396.38</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>383.03</v>
+        <v>384.58</v>
       </c>
       <c r="L26" s="23" t="n">
-        <v>390.41</v>
+        <v>383.59</v>
       </c>
       <c r="M26" s="24" t="n">
-        <v>377.02</v>
+        <v>391.28</v>
       </c>
     </row>
     <row r="27">
@@ -8014,25 +8014,25 @@
         <v>400</v>
       </c>
       <c r="G27" s="23" t="n">
-        <v>389.99</v>
+        <v>389.4</v>
       </c>
       <c r="H27" s="24" t="n">
-        <v>371.62</v>
+        <v>371.32</v>
       </c>
       <c r="I27" s="23" t="n">
-        <v>401.82</v>
+        <v>389.32</v>
       </c>
       <c r="J27" s="23" t="n">
-        <v>398.59</v>
+        <v>401.93</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>390.32</v>
+        <v>393.77</v>
       </c>
       <c r="L27" s="23" t="n">
-        <v>396.21</v>
+        <v>388.55</v>
       </c>
       <c r="M27" s="24" t="n">
-        <v>379.61</v>
+        <v>390.41</v>
       </c>
     </row>
     <row r="28">
@@ -8055,25 +8055,25 @@
         <v>400</v>
       </c>
       <c r="G28" s="23" t="n">
-        <v>396.56</v>
+        <v>397.19</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>382.4</v>
+        <v>382.05</v>
       </c>
       <c r="I28" s="23" t="n">
-        <v>400.47</v>
+        <v>400.72</v>
       </c>
       <c r="J28" s="23" t="n">
-        <v>400.11</v>
+        <v>401.75</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>395.35</v>
+        <v>396.55</v>
       </c>
       <c r="L28" s="23" t="n">
-        <v>409.21</v>
+        <v>400.05</v>
       </c>
       <c r="M28" s="24" t="n">
-        <v>390.47</v>
+        <v>400.77</v>
       </c>
     </row>
     <row r="29">
@@ -8096,25 +8096,25 @@
         <v>400</v>
       </c>
       <c r="G29" s="23" t="n">
-        <v>395.5</v>
+        <v>396.41</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>384.38</v>
+        <v>384.04</v>
       </c>
       <c r="I29" s="23" t="n">
-        <v>395.88</v>
+        <v>397.28</v>
       </c>
       <c r="J29" s="23" t="n">
-        <v>394.25</v>
+        <v>398.1</v>
       </c>
       <c r="K29" s="24" t="n">
-        <v>396.63</v>
+        <v>397.66</v>
       </c>
       <c r="L29" s="23" t="n">
-        <v>405.57</v>
+        <v>400.47</v>
       </c>
       <c r="M29" s="24" t="n">
-        <v>395.18</v>
+        <v>399.86</v>
       </c>
     </row>
     <row r="30">
@@ -8137,25 +8137,25 @@
         <v>399.99</v>
       </c>
       <c r="G30" s="23" t="n">
-        <v>393.85</v>
+        <v>392.63</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>375.65</v>
+        <v>375.26</v>
       </c>
       <c r="I30" s="23" t="n">
-        <v>404.72</v>
+        <v>393.7</v>
       </c>
       <c r="J30" s="23" t="n">
-        <v>390.23</v>
+        <v>395.07</v>
       </c>
       <c r="K30" s="24" t="n">
-        <v>394.42</v>
+        <v>395.13</v>
       </c>
       <c r="L30" s="23" t="n">
-        <v>403.05</v>
+        <v>397.48</v>
       </c>
       <c r="M30" s="24" t="n">
-        <v>392.91</v>
+        <v>397.68</v>
       </c>
     </row>
     <row r="31">
@@ -8178,25 +8178,25 @@
         <v>399.99</v>
       </c>
       <c r="G31" s="23" t="n">
-        <v>369.81</v>
+        <v>368.58</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>343.73</v>
+        <v>343.27</v>
       </c>
       <c r="I31" s="23" t="n">
-        <v>381.26</v>
+        <v>366.61</v>
       </c>
       <c r="J31" s="23" t="n">
-        <v>388.92</v>
+        <v>392.81</v>
       </c>
       <c r="K31" s="24" t="n">
-        <v>379.32</v>
+        <v>378.09</v>
       </c>
       <c r="L31" s="23" t="n">
-        <v>360.76</v>
+        <v>362.18</v>
       </c>
       <c r="M31" s="24" t="n">
-        <v>362.78</v>
+        <v>367.3</v>
       </c>
     </row>
     <row r="32">
@@ -8219,25 +8219,25 @@
         <v>399.99</v>
       </c>
       <c r="G32" s="23" t="n">
-        <v>350.24</v>
+        <v>348.38</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>318.98</v>
+        <v>318.52</v>
       </c>
       <c r="I32" s="23" t="n">
-        <v>358.14</v>
+        <v>349</v>
       </c>
       <c r="J32" s="23" t="n">
-        <v>378.62</v>
+        <v>381.26</v>
       </c>
       <c r="K32" s="24" t="n">
-        <v>371.24</v>
+        <v>366.18</v>
       </c>
       <c r="L32" s="23" t="n">
-        <v>336.3</v>
+        <v>336.8</v>
       </c>
       <c r="M32" s="24" t="n">
-        <v>336.04</v>
+        <v>337.27</v>
       </c>
     </row>
     <row r="33">
@@ -8260,25 +8260,25 @@
         <v>399.99</v>
       </c>
       <c r="G33" s="23" t="n">
-        <v>351.78</v>
+        <v>345.36</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>307.9</v>
+        <v>307.4</v>
       </c>
       <c r="I33" s="23" t="n">
-        <v>344.61</v>
+        <v>333.96</v>
       </c>
       <c r="J33" s="23" t="n">
-        <v>376.86</v>
+        <v>369.91</v>
       </c>
       <c r="K33" s="24" t="n">
-        <v>376.72</v>
+        <v>372.9</v>
       </c>
       <c r="L33" s="23" t="n">
-        <v>351.01</v>
+        <v>338.36</v>
       </c>
       <c r="M33" s="24" t="n">
-        <v>350.51</v>
+        <v>347.49</v>
       </c>
     </row>
     <row r="34">
@@ -8301,25 +8301,25 @@
         <v>295.9</v>
       </c>
       <c r="G34" s="23" t="n">
-        <v>333.41</v>
+        <v>325.38</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>285.9</v>
+        <v>285.38</v>
       </c>
       <c r="I34" s="23" t="n">
-        <v>350.4</v>
+        <v>322.51</v>
       </c>
       <c r="J34" s="23" t="n">
-        <v>341.79</v>
+        <v>338.79</v>
       </c>
       <c r="K34" s="24" t="n">
-        <v>363.5</v>
+        <v>357</v>
       </c>
       <c r="L34" s="23" t="n">
-        <v>321</v>
+        <v>314.77</v>
       </c>
       <c r="M34" s="24" t="n">
-        <v>333.36</v>
+        <v>331.02</v>
       </c>
     </row>
     <row r="35">
@@ -8342,25 +8342,25 @@
         <v>295.9</v>
       </c>
       <c r="G35" s="23" t="n">
-        <v>312.8</v>
+        <v>310.97</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>265.59</v>
+        <v>265.13</v>
       </c>
       <c r="I35" s="23" t="n">
-        <v>306.04</v>
+        <v>315.25</v>
       </c>
       <c r="J35" s="23" t="n">
-        <v>336.39</v>
+        <v>329.78</v>
       </c>
       <c r="K35" s="24" t="n">
-        <v>331.08</v>
+        <v>331.39</v>
       </c>
       <c r="L35" s="23" t="n">
-        <v>314.99</v>
+        <v>306.32</v>
       </c>
       <c r="M35" s="24" t="n">
-        <v>319.16</v>
+        <v>314.69</v>
       </c>
     </row>
     <row r="36">
@@ -8383,25 +8383,25 @@
         <v>295.9</v>
       </c>
       <c r="G36" s="23" t="n">
-        <v>270.76</v>
+        <v>262.2</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>228.68</v>
+        <v>228.13</v>
       </c>
       <c r="I36" s="23" t="n">
-        <v>285.87</v>
+        <v>269.61</v>
       </c>
       <c r="J36" s="23" t="n">
-        <v>306.81</v>
+        <v>304.94</v>
       </c>
       <c r="K36" s="24" t="n">
-        <v>278.76</v>
+        <v>273.65</v>
       </c>
       <c r="L36" s="23" t="n">
-        <v>248.84</v>
+        <v>245.3</v>
       </c>
       <c r="M36" s="24" t="n">
-        <v>272.46</v>
+        <v>250.29</v>
       </c>
     </row>
     <row r="37">
@@ -8424,25 +8424,25 @@
         <v>295.9</v>
       </c>
       <c r="G37" s="23" t="n">
-        <v>236.29</v>
+        <v>221.16</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>198.4</v>
+        <v>197.83</v>
       </c>
       <c r="I37" s="23" t="n">
-        <v>232.25</v>
+        <v>215.58</v>
       </c>
       <c r="J37" s="23" t="n">
-        <v>276.39</v>
+        <v>244.76</v>
       </c>
       <c r="K37" s="24" t="n">
-        <v>265.35</v>
+        <v>258.34</v>
       </c>
       <c r="L37" s="23" t="n">
-        <v>185.62</v>
+        <v>179.32</v>
       </c>
       <c r="M37" s="24" t="n">
-        <v>257.72</v>
+        <v>230.38</v>
       </c>
     </row>
     <row r="38">
@@ -8456,7 +8456,7 @@
         <v>10</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>170</v>
+        <v>170.5</v>
       </c>
       <c r="E38" s="13" t="n">
         <v>138.99</v>
@@ -8465,25 +8465,25 @@
         <v>200.01</v>
       </c>
       <c r="G38" s="23" t="n">
-        <v>165.15</v>
+        <v>170.15</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>165.13</v>
+        <v>164.52</v>
       </c>
       <c r="I38" s="23" t="n">
-        <v>158.61</v>
+        <v>178.98</v>
       </c>
       <c r="J38" s="23" t="n">
-        <v>143</v>
+        <v>133.71</v>
       </c>
       <c r="K38" s="24" t="n">
-        <v>212.12</v>
+        <v>203.09</v>
       </c>
       <c r="L38" s="23" t="n">
-        <v>105.01</v>
+        <v>127.01</v>
       </c>
       <c r="M38" s="24" t="n">
-        <v>206.72</v>
+        <v>211.94</v>
       </c>
     </row>
     <row r="39">
@@ -8497,7 +8497,7 @@
         <v>10</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>170</v>
+        <v>170.5</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>138.99</v>
@@ -8506,25 +8506,25 @@
         <v>200.01</v>
       </c>
       <c r="G39" s="23" t="n">
-        <v>157.43</v>
+        <v>157.07</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>148.87</v>
+        <v>148.32</v>
       </c>
       <c r="I39" s="23" t="n">
-        <v>138.59</v>
+        <v>154.88</v>
       </c>
       <c r="J39" s="23" t="n">
-        <v>163.69</v>
+        <v>168.86</v>
       </c>
       <c r="K39" s="24" t="n">
-        <v>210.05</v>
+        <v>194.03</v>
       </c>
       <c r="L39" s="23" t="n">
-        <v>102.28</v>
+        <v>100.43</v>
       </c>
       <c r="M39" s="24" t="n">
-        <v>181.24</v>
+        <v>176.02</v>
       </c>
     </row>
     <row r="40">
@@ -8538,7 +8538,7 @@
         <v>10</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>170</v>
+        <v>170.5</v>
       </c>
       <c r="E40" s="13" t="n">
         <v>138.99</v>
@@ -8547,25 +8547,25 @@
         <v>200.01</v>
       </c>
       <c r="G40" s="23" t="n">
-        <v>140.15</v>
+        <v>141.48</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>129.03</v>
+        <v>128.49</v>
       </c>
       <c r="I40" s="23" t="n">
-        <v>128.27</v>
+        <v>119.09</v>
       </c>
       <c r="J40" s="23" t="n">
-        <v>169.34</v>
+        <v>169.69</v>
       </c>
       <c r="K40" s="24" t="n">
-        <v>187.08</v>
+        <v>173.53</v>
       </c>
       <c r="L40" s="23" t="n">
-        <v>70.48</v>
+        <v>97.78</v>
       </c>
       <c r="M40" s="24" t="n">
-        <v>157.24</v>
+        <v>160.78</v>
       </c>
     </row>
     <row r="41">
@@ -8579,7 +8579,7 @@
         <v>10</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>170</v>
+        <v>170.5</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>138.99</v>
@@ -8588,25 +8588,25 @@
         <v>200.01</v>
       </c>
       <c r="G41" s="23" t="n">
-        <v>123.7</v>
+        <v>125.74</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>111.17</v>
+        <v>110.63</v>
       </c>
       <c r="I41" s="23" t="n">
-        <v>122.72</v>
+        <v>103.87</v>
       </c>
       <c r="J41" s="23" t="n">
-        <v>146.51</v>
+        <v>171.08</v>
       </c>
       <c r="K41" s="24" t="n">
-        <v>182.92</v>
+        <v>163.33</v>
       </c>
       <c r="L41" s="23" t="n">
-        <v>46.03</v>
+        <v>81.55</v>
       </c>
       <c r="M41" s="24" t="n">
-        <v>132.85</v>
+        <v>124.99</v>
       </c>
     </row>
     <row r="42">
@@ -8629,25 +8629,25 @@
         <v>200</v>
       </c>
       <c r="G42" s="23" t="n">
-        <v>116</v>
+        <v>123.83</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>104.21</v>
+        <v>103.65</v>
       </c>
       <c r="I42" s="23" t="n">
-        <v>117.96</v>
+        <v>105.23</v>
       </c>
       <c r="J42" s="23" t="n">
-        <v>135.97</v>
+        <v>166.07</v>
       </c>
       <c r="K42" s="24" t="n">
-        <v>181.76</v>
+        <v>165.34</v>
       </c>
       <c r="L42" s="23" t="n">
-        <v>38.87</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="M42" s="24" t="n">
-        <v>117.19</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="43">
@@ -8670,25 +8670,25 @@
         <v>200</v>
       </c>
       <c r="G43" s="23" t="n">
-        <v>108.65</v>
+        <v>110.22</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>92.09999999999999</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="I43" s="23" t="n">
-        <v>106.96</v>
+        <v>86.61</v>
       </c>
       <c r="J43" s="23" t="n">
-        <v>136.6</v>
+        <v>157.09</v>
       </c>
       <c r="K43" s="24" t="n">
-        <v>176.78</v>
+        <v>154.62</v>
       </c>
       <c r="L43" s="23" t="n">
-        <v>39.97</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="M43" s="24" t="n">
-        <v>99.37</v>
+        <v>102.02</v>
       </c>
     </row>
     <row r="44">
@@ -8711,25 +8711,25 @@
         <v>200</v>
       </c>
       <c r="G44" s="23" t="n">
-        <v>100.2</v>
+        <v>103.21</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>87.87</v>
+        <v>87.3</v>
       </c>
       <c r="I44" s="23" t="n">
-        <v>96.27</v>
+        <v>89.36</v>
       </c>
       <c r="J44" s="23" t="n">
-        <v>139.14</v>
+        <v>148.31</v>
       </c>
       <c r="K44" s="24" t="n">
-        <v>155.7</v>
+        <v>140.1</v>
       </c>
       <c r="L44" s="23" t="n">
-        <v>27.3</v>
+        <v>53.83</v>
       </c>
       <c r="M44" s="24" t="n">
-        <v>95.54000000000001</v>
+        <v>101.21</v>
       </c>
     </row>
     <row r="45">
@@ -8752,25 +8752,25 @@
         <v>200</v>
       </c>
       <c r="G45" s="23" t="n">
-        <v>100.62</v>
+        <v>103.37</v>
       </c>
       <c r="H45" s="24" t="n">
-        <v>88.52</v>
+        <v>87.97</v>
       </c>
       <c r="I45" s="23" t="n">
-        <v>102.08</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="J45" s="23" t="n">
-        <v>139.14</v>
+        <v>148.31</v>
       </c>
       <c r="K45" s="24" t="n">
-        <v>153.89</v>
+        <v>134.18</v>
       </c>
       <c r="L45" s="23" t="n">
-        <v>25.65</v>
+        <v>49.5</v>
       </c>
       <c r="M45" s="24" t="n">
-        <v>94.95</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="46">
@@ -8793,25 +8793,25 @@
         <v>199</v>
       </c>
       <c r="G46" s="23" t="n">
-        <v>120.03</v>
+        <v>127.02</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>125.9</v>
+        <v>125.44</v>
       </c>
       <c r="I46" s="23" t="n">
-        <v>107.92</v>
+        <v>116.33</v>
       </c>
       <c r="J46" s="23" t="n">
-        <v>148.45</v>
+        <v>158.59</v>
       </c>
       <c r="K46" s="24" t="n">
-        <v>195.81</v>
+        <v>181.18</v>
       </c>
       <c r="L46" s="23" t="n">
-        <v>38.57</v>
+        <v>52.93</v>
       </c>
       <c r="M46" s="24" t="n">
-        <v>105.89</v>
+        <v>129.46</v>
       </c>
     </row>
     <row r="47">
@@ -8834,25 +8834,25 @@
         <v>199</v>
       </c>
       <c r="G47" s="23" t="n">
-        <v>131.83</v>
+        <v>137.88</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>120.81</v>
+        <v>120.2</v>
       </c>
       <c r="I47" s="23" t="n">
-        <v>103.7</v>
+        <v>115.02</v>
       </c>
       <c r="J47" s="23" t="n">
-        <v>143.79</v>
+        <v>172.55</v>
       </c>
       <c r="K47" s="24" t="n">
-        <v>206.12</v>
+        <v>182.47</v>
       </c>
       <c r="L47" s="23" t="n">
-        <v>69.27</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="M47" s="24" t="n">
-        <v>147.74</v>
+        <v>155.48</v>
       </c>
     </row>
     <row r="48">
@@ -8875,25 +8875,25 @@
         <v>199</v>
       </c>
       <c r="G48" s="23" t="n">
-        <v>127.55</v>
+        <v>127.75</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>117.83</v>
+        <v>117.22</v>
       </c>
       <c r="I48" s="23" t="n">
-        <v>120.05</v>
+        <v>98.23999999999999</v>
       </c>
       <c r="J48" s="23" t="n">
-        <v>140.47</v>
+        <v>149.09</v>
       </c>
       <c r="K48" s="24" t="n">
-        <v>197.22</v>
+        <v>180.07</v>
       </c>
       <c r="L48" s="23" t="n">
-        <v>58.54</v>
+        <v>79.75</v>
       </c>
       <c r="M48" s="24" t="n">
-        <v>131.32</v>
+        <v>142.75</v>
       </c>
     </row>
     <row r="49">
@@ -8916,25 +8916,25 @@
         <v>199</v>
       </c>
       <c r="G49" s="23" t="n">
-        <v>117.72</v>
+        <v>120.21</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>93.53</v>
+        <v>92.86</v>
       </c>
       <c r="I49" s="23" t="n">
-        <v>124.49</v>
+        <v>110.65</v>
       </c>
       <c r="J49" s="23" t="n">
-        <v>132.58</v>
+        <v>147.48</v>
       </c>
       <c r="K49" s="24" t="n">
-        <v>181.51</v>
+        <v>158.81</v>
       </c>
       <c r="L49" s="23" t="n">
-        <v>48.26</v>
+        <v>74.69</v>
       </c>
       <c r="M49" s="24" t="n">
-        <v>124.36</v>
+        <v>135.86</v>
       </c>
     </row>
     <row r="50">
@@ -8957,25 +8957,25 @@
         <v>300</v>
       </c>
       <c r="G50" s="23" t="n">
-        <v>131.51</v>
+        <v>128.34</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>108.3</v>
+        <v>107.7</v>
       </c>
       <c r="I50" s="23" t="n">
-        <v>145.7</v>
+        <v>112.9</v>
       </c>
       <c r="J50" s="23" t="n">
-        <v>132.93</v>
+        <v>140.53</v>
       </c>
       <c r="K50" s="24" t="n">
-        <v>197.18</v>
+        <v>172.13</v>
       </c>
       <c r="L50" s="23" t="n">
-        <v>61.08</v>
+        <v>91.39</v>
       </c>
       <c r="M50" s="24" t="n">
-        <v>141.77</v>
+        <v>144.56</v>
       </c>
     </row>
     <row r="51">
@@ -8998,25 +8998,25 @@
         <v>300</v>
       </c>
       <c r="G51" s="23" t="n">
-        <v>130.03</v>
+        <v>130.96</v>
       </c>
       <c r="H51" s="24" t="n">
-        <v>109.47</v>
+        <v>108.86</v>
       </c>
       <c r="I51" s="23" t="n">
-        <v>131.93</v>
+        <v>117</v>
       </c>
       <c r="J51" s="23" t="n">
-        <v>135.59</v>
+        <v>144.59</v>
       </c>
       <c r="K51" s="24" t="n">
-        <v>195.82</v>
+        <v>173.07</v>
       </c>
       <c r="L51" s="23" t="n">
-        <v>67.44</v>
+        <v>95.87</v>
       </c>
       <c r="M51" s="24" t="n">
-        <v>138.53</v>
+        <v>145.44</v>
       </c>
     </row>
     <row r="52">
@@ -9039,25 +9039,25 @@
         <v>300</v>
       </c>
       <c r="G52" s="23" t="n">
-        <v>139.41</v>
+        <v>139.03</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>114.05</v>
+        <v>113.45</v>
       </c>
       <c r="I52" s="23" t="n">
-        <v>151.82</v>
+        <v>130.15</v>
       </c>
       <c r="J52" s="23" t="n">
-        <v>142.62</v>
+        <v>151.37</v>
       </c>
       <c r="K52" s="24" t="n">
-        <v>198.52</v>
+        <v>174.88</v>
       </c>
       <c r="L52" s="23" t="n">
-        <v>81.72</v>
+        <v>116.37</v>
       </c>
       <c r="M52" s="24" t="n">
-        <v>145.53</v>
+        <v>146.53</v>
       </c>
     </row>
     <row r="53">
@@ -9080,25 +9080,25 @@
         <v>300</v>
       </c>
       <c r="G53" s="23" t="n">
-        <v>153.48</v>
+        <v>152.33</v>
       </c>
       <c r="H53" s="24" t="n">
-        <v>129.97</v>
+        <v>129.42</v>
       </c>
       <c r="I53" s="23" t="n">
-        <v>170.4</v>
+        <v>153.33</v>
       </c>
       <c r="J53" s="23" t="n">
-        <v>170.64</v>
+        <v>159.83</v>
       </c>
       <c r="K53" s="24" t="n">
-        <v>203.6</v>
+        <v>186.54</v>
       </c>
       <c r="L53" s="23" t="n">
-        <v>93.77</v>
+        <v>121.04</v>
       </c>
       <c r="M53" s="24" t="n">
-        <v>150.76</v>
+        <v>162.39</v>
       </c>
     </row>
     <row r="54">
@@ -9121,25 +9121,25 @@
         <v>205</v>
       </c>
       <c r="G54" s="23" t="n">
-        <v>158.41</v>
+        <v>161.83</v>
       </c>
       <c r="H54" s="24" t="n">
-        <v>157.3</v>
+        <v>156.77</v>
       </c>
       <c r="I54" s="23" t="n">
-        <v>174.24</v>
+        <v>189.37</v>
       </c>
       <c r="J54" s="23" t="n">
-        <v>185.27</v>
+        <v>150.51</v>
       </c>
       <c r="K54" s="24" t="n">
-        <v>222.48</v>
+        <v>209.84</v>
       </c>
       <c r="L54" s="23" t="n">
-        <v>72.34</v>
+        <v>89.59</v>
       </c>
       <c r="M54" s="24" t="n">
-        <v>139.77</v>
+        <v>174.4</v>
       </c>
     </row>
     <row r="55">
@@ -9162,25 +9162,25 @@
         <v>205</v>
       </c>
       <c r="G55" s="23" t="n">
-        <v>191.46</v>
+        <v>197.51</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>185.29</v>
+        <v>184.84</v>
       </c>
       <c r="I55" s="23" t="n">
-        <v>180.18</v>
+        <v>193.84</v>
       </c>
       <c r="J55" s="23" t="n">
-        <v>236.54</v>
+        <v>245.92</v>
       </c>
       <c r="K55" s="24" t="n">
-        <v>266.14</v>
+        <v>255.67</v>
       </c>
       <c r="L55" s="23" t="n">
-        <v>110.87</v>
+        <v>115.47</v>
       </c>
       <c r="M55" s="24" t="n">
-        <v>171.46</v>
+        <v>190.84</v>
       </c>
     </row>
     <row r="56">
@@ -9203,25 +9203,25 @@
         <v>205</v>
       </c>
       <c r="G56" s="23" t="n">
-        <v>231.59</v>
+        <v>229.37</v>
       </c>
       <c r="H56" s="24" t="n">
-        <v>205.98</v>
+        <v>205.5</v>
       </c>
       <c r="I56" s="23" t="n">
-        <v>211.1</v>
+        <v>220.03</v>
       </c>
       <c r="J56" s="23" t="n">
-        <v>277.76</v>
+        <v>280.02</v>
       </c>
       <c r="K56" s="24" t="n">
-        <v>293.29</v>
+        <v>274.82</v>
       </c>
       <c r="L56" s="23" t="n">
-        <v>185.56</v>
+        <v>170.42</v>
       </c>
       <c r="M56" s="24" t="n">
-        <v>215.8</v>
+        <v>225.89</v>
       </c>
     </row>
     <row r="57">
@@ -9244,25 +9244,25 @@
         <v>205</v>
       </c>
       <c r="G57" s="23" t="n">
-        <v>242.79</v>
+        <v>245.42</v>
       </c>
       <c r="H57" s="24" t="n">
-        <v>232.15</v>
+        <v>231.72</v>
       </c>
       <c r="I57" s="23" t="n">
-        <v>234.44</v>
+        <v>231.78</v>
       </c>
       <c r="J57" s="23" t="n">
-        <v>274.75</v>
+        <v>283.85</v>
       </c>
       <c r="K57" s="24" t="n">
-        <v>298.78</v>
+        <v>289.25</v>
       </c>
       <c r="L57" s="23" t="n">
-        <v>192.78</v>
+        <v>191.47</v>
       </c>
       <c r="M57" s="24" t="n">
-        <v>224.45</v>
+        <v>245.32</v>
       </c>
     </row>
     <row r="58">
@@ -9285,25 +9285,25 @@
         <v>300.1</v>
       </c>
       <c r="G58" s="23" t="n">
-        <v>300.61</v>
+        <v>297.14</v>
       </c>
       <c r="H58" s="24" t="n">
-        <v>255.62</v>
+        <v>255.09</v>
       </c>
       <c r="I58" s="23" t="n">
-        <v>304.04</v>
+        <v>288.08</v>
       </c>
       <c r="J58" s="23" t="n">
-        <v>335.94</v>
+        <v>331.6</v>
       </c>
       <c r="K58" s="24" t="n">
-        <v>346.03</v>
+        <v>338.07</v>
       </c>
       <c r="L58" s="23" t="n">
-        <v>274.15</v>
+        <v>274.36</v>
       </c>
       <c r="M58" s="24" t="n">
-        <v>284.93</v>
+        <v>293.63</v>
       </c>
     </row>
     <row r="59">
@@ -9326,25 +9326,25 @@
         <v>300.1</v>
       </c>
       <c r="G59" s="23" t="n">
-        <v>322.57</v>
+        <v>326.65</v>
       </c>
       <c r="H59" s="24" t="n">
-        <v>280.87</v>
+        <v>280.32</v>
       </c>
       <c r="I59" s="23" t="n">
-        <v>331.3</v>
+        <v>326.59</v>
       </c>
       <c r="J59" s="23" t="n">
-        <v>342.46</v>
+        <v>342.84</v>
       </c>
       <c r="K59" s="24" t="n">
-        <v>361.32</v>
+        <v>363.89</v>
       </c>
       <c r="L59" s="23" t="n">
-        <v>312.17</v>
+        <v>314.44</v>
       </c>
       <c r="M59" s="24" t="n">
-        <v>303.97</v>
+        <v>328.61</v>
       </c>
     </row>
     <row r="60">
@@ -9367,25 +9367,25 @@
         <v>300.1</v>
       </c>
       <c r="G60" s="23" t="n">
-        <v>340.06</v>
+        <v>342.84</v>
       </c>
       <c r="H60" s="24" t="n">
-        <v>305.56</v>
+        <v>305.02</v>
       </c>
       <c r="I60" s="23" t="n">
-        <v>352.24</v>
+        <v>345.82</v>
       </c>
       <c r="J60" s="23" t="n">
-        <v>355.65</v>
+        <v>355.42</v>
       </c>
       <c r="K60" s="24" t="n">
-        <v>370.01</v>
+        <v>368.15</v>
       </c>
       <c r="L60" s="23" t="n">
-        <v>334.09</v>
+        <v>336.29</v>
       </c>
       <c r="M60" s="24" t="n">
-        <v>319.92</v>
+        <v>343.61</v>
       </c>
     </row>
     <row r="61">
@@ -9408,25 +9408,25 @@
         <v>300.1</v>
       </c>
       <c r="G61" s="23" t="n">
-        <v>360.85</v>
+        <v>363.11</v>
       </c>
       <c r="H61" s="24" t="n">
-        <v>316.66</v>
+        <v>316.08</v>
       </c>
       <c r="I61" s="23" t="n">
-        <v>365.04</v>
+        <v>372.9</v>
       </c>
       <c r="J61" s="23" t="n">
-        <v>373.75</v>
+        <v>373.35</v>
       </c>
       <c r="K61" s="24" t="n">
-        <v>384.8</v>
+        <v>381.07</v>
       </c>
       <c r="L61" s="23" t="n">
-        <v>362.62</v>
+        <v>362.94</v>
       </c>
       <c r="M61" s="24" t="n">
-        <v>358.44</v>
+        <v>368.54</v>
       </c>
     </row>
     <row r="62">
@@ -9449,25 +9449,25 @@
         <v>400</v>
       </c>
       <c r="G62" s="23" t="n">
-        <v>370.91</v>
+        <v>375.27</v>
       </c>
       <c r="H62" s="24" t="n">
-        <v>346.48</v>
+        <v>345.96</v>
       </c>
       <c r="I62" s="23" t="n">
-        <v>359.35</v>
+        <v>373.38</v>
       </c>
       <c r="J62" s="23" t="n">
-        <v>383.09</v>
+        <v>382.29</v>
       </c>
       <c r="K62" s="24" t="n">
-        <v>392.08</v>
+        <v>390.11</v>
       </c>
       <c r="L62" s="23" t="n">
-        <v>376.69</v>
+        <v>370.4</v>
       </c>
       <c r="M62" s="24" t="n">
-        <v>366.17</v>
+        <v>387.22</v>
       </c>
     </row>
     <row r="63">
@@ -9490,25 +9490,25 @@
         <v>400</v>
       </c>
       <c r="G63" s="23" t="n">
-        <v>390.35</v>
+        <v>391.62</v>
       </c>
       <c r="H63" s="24" t="n">
-        <v>363.76</v>
+        <v>363.27</v>
       </c>
       <c r="I63" s="23" t="n">
-        <v>402.43</v>
+        <v>404.72</v>
       </c>
       <c r="J63" s="23" t="n">
-        <v>392.2</v>
+        <v>388.44</v>
       </c>
       <c r="K63" s="24" t="n">
-        <v>396.7</v>
+        <v>396.45</v>
       </c>
       <c r="L63" s="23" t="n">
-        <v>398.73</v>
+        <v>398.74</v>
       </c>
       <c r="M63" s="24" t="n">
-        <v>385.5</v>
+        <v>395.34</v>
       </c>
     </row>
     <row r="64">
@@ -9531,25 +9531,25 @@
         <v>400</v>
       </c>
       <c r="G64" s="23" t="n">
-        <v>406.11</v>
+        <v>408.62</v>
       </c>
       <c r="H64" s="24" t="n">
-        <v>394.14</v>
+        <v>393.71</v>
       </c>
       <c r="I64" s="23" t="n">
-        <v>407.32</v>
+        <v>411.52</v>
       </c>
       <c r="J64" s="23" t="n">
-        <v>393.71</v>
+        <v>395.6</v>
       </c>
       <c r="K64" s="24" t="n">
-        <v>409.59</v>
+        <v>409.01</v>
       </c>
       <c r="L64" s="23" t="n">
-        <v>422.27</v>
+        <v>426.14</v>
       </c>
       <c r="M64" s="24" t="n">
-        <v>408.04</v>
+        <v>413.81</v>
       </c>
     </row>
     <row r="65">
@@ -9572,25 +9572,25 @@
         <v>400</v>
       </c>
       <c r="G65" s="23" t="n">
-        <v>431.16</v>
+        <v>434.43</v>
       </c>
       <c r="H65" s="24" t="n">
-        <v>431.92</v>
+        <v>431.48</v>
       </c>
       <c r="I65" s="23" t="n">
-        <v>439.69</v>
+        <v>442.04</v>
       </c>
       <c r="J65" s="23" t="n">
-        <v>410.95</v>
+        <v>414.82</v>
       </c>
       <c r="K65" s="24" t="n">
-        <v>427.92</v>
+        <v>430.99</v>
       </c>
       <c r="L65" s="23" t="n">
-        <v>442.03</v>
+        <v>449.91</v>
       </c>
       <c r="M65" s="24" t="n">
-        <v>433.62</v>
+        <v>436.17</v>
       </c>
     </row>
     <row r="66">
@@ -9613,25 +9613,25 @@
         <v>435</v>
       </c>
       <c r="G66" s="23" t="n">
-        <v>434.88</v>
+        <v>439.72</v>
       </c>
       <c r="H66" s="24" t="n">
-        <v>443.29</v>
+        <v>443.12</v>
       </c>
       <c r="I66" s="23" t="n">
-        <v>438.76</v>
+        <v>451.1</v>
       </c>
       <c r="J66" s="23" t="n">
-        <v>413.88</v>
+        <v>419.11</v>
       </c>
       <c r="K66" s="24" t="n">
-        <v>436.97</v>
+        <v>439.88</v>
       </c>
       <c r="L66" s="23" t="n">
-        <v>448.74</v>
+        <v>450.35</v>
       </c>
       <c r="M66" s="24" t="n">
-        <v>427.67</v>
+        <v>434.13</v>
       </c>
     </row>
     <row r="67">
@@ -9654,25 +9654,25 @@
         <v>435</v>
       </c>
       <c r="G67" s="23" t="n">
-        <v>439.09</v>
+        <v>442.63</v>
       </c>
       <c r="H67" s="24" t="n">
-        <v>454.57</v>
+        <v>454.31</v>
       </c>
       <c r="I67" s="23" t="n">
-        <v>439.87</v>
+        <v>451.41</v>
       </c>
       <c r="J67" s="23" t="n">
-        <v>417.66</v>
+        <v>422.42</v>
       </c>
       <c r="K67" s="24" t="n">
-        <v>437.88</v>
+        <v>437.52</v>
       </c>
       <c r="L67" s="23" t="n">
-        <v>444.04</v>
+        <v>443.77</v>
       </c>
       <c r="M67" s="24" t="n">
-        <v>441.29</v>
+        <v>446.5</v>
       </c>
     </row>
     <row r="68">
@@ -9695,25 +9695,25 @@
         <v>435</v>
       </c>
       <c r="G68" s="23" t="n">
-        <v>453.29</v>
+        <v>452.99</v>
       </c>
       <c r="H68" s="24" t="n">
-        <v>470.41</v>
+        <v>470.17</v>
       </c>
       <c r="I68" s="23" t="n">
-        <v>450.86</v>
+        <v>452.14</v>
       </c>
       <c r="J68" s="23" t="n">
-        <v>424.34</v>
+        <v>423.57</v>
       </c>
       <c r="K68" s="24" t="n">
-        <v>442.32</v>
+        <v>439.9</v>
       </c>
       <c r="L68" s="23" t="n">
-        <v>465.49</v>
+        <v>466.67</v>
       </c>
       <c r="M68" s="24" t="n">
-        <v>466.96</v>
+        <v>465.77</v>
       </c>
     </row>
     <row r="69">
@@ -9736,25 +9736,25 @@
         <v>435</v>
       </c>
       <c r="G69" s="23" t="n">
-        <v>453.3</v>
+        <v>454.88</v>
       </c>
       <c r="H69" s="24" t="n">
-        <v>477.15</v>
+        <v>476.93</v>
       </c>
       <c r="I69" s="23" t="n">
-        <v>457.46</v>
+        <v>461.87</v>
       </c>
       <c r="J69" s="23" t="n">
-        <v>426.23</v>
+        <v>425.77</v>
       </c>
       <c r="K69" s="24" t="n">
-        <v>439.95</v>
+        <v>440.05</v>
       </c>
       <c r="L69" s="23" t="n">
-        <v>462.4</v>
+        <v>460.94</v>
       </c>
       <c r="M69" s="24" t="n">
-        <v>457.82</v>
+        <v>464.39</v>
       </c>
     </row>
     <row r="70">
@@ -9777,25 +9777,25 @@
         <v>439.1</v>
       </c>
       <c r="G70" s="23" t="n">
-        <v>457.24</v>
+        <v>456.61</v>
       </c>
       <c r="H70" s="24" t="n">
-        <v>475.97</v>
+        <v>475.64</v>
       </c>
       <c r="I70" s="23" t="n">
-        <v>460.2</v>
+        <v>462.83</v>
       </c>
       <c r="J70" s="23" t="n">
-        <v>446.59</v>
+        <v>444.05</v>
       </c>
       <c r="K70" s="24" t="n">
-        <v>441.6</v>
+        <v>438.61</v>
       </c>
       <c r="L70" s="23" t="n">
-        <v>467.08</v>
+        <v>463.09</v>
       </c>
       <c r="M70" s="24" t="n">
-        <v>453.31</v>
+        <v>456.45</v>
       </c>
     </row>
     <row r="71">
@@ -9818,25 +9818,25 @@
         <v>439.1</v>
       </c>
       <c r="G71" s="23" t="n">
-        <v>460.27</v>
+        <v>459.28</v>
       </c>
       <c r="H71" s="24" t="n">
-        <v>483.17</v>
+        <v>482.87</v>
       </c>
       <c r="I71" s="23" t="n">
-        <v>469.41</v>
+        <v>470.8</v>
       </c>
       <c r="J71" s="23" t="n">
-        <v>446.03</v>
+        <v>443.49</v>
       </c>
       <c r="K71" s="24" t="n">
-        <v>442.16</v>
+        <v>440.85</v>
       </c>
       <c r="L71" s="23" t="n">
-        <v>468.39</v>
+        <v>462.72</v>
       </c>
       <c r="M71" s="24" t="n">
-        <v>453.87</v>
+        <v>456.23</v>
       </c>
     </row>
     <row r="72">
@@ -9859,25 +9859,25 @@
         <v>439.1</v>
       </c>
       <c r="G72" s="23" t="n">
-        <v>459.92</v>
+        <v>460.01</v>
       </c>
       <c r="H72" s="24" t="n">
-        <v>485.4</v>
+        <v>485.05</v>
       </c>
       <c r="I72" s="23" t="n">
-        <v>465.1</v>
+        <v>468.04</v>
       </c>
       <c r="J72" s="23" t="n">
-        <v>446.03</v>
+        <v>443.28</v>
       </c>
       <c r="K72" s="24" t="n">
-        <v>442.53</v>
+        <v>440.79</v>
       </c>
       <c r="L72" s="23" t="n">
-        <v>468.48</v>
+        <v>469.88</v>
       </c>
       <c r="M72" s="24" t="n">
-        <v>453.74</v>
+        <v>454.36</v>
       </c>
     </row>
     <row r="73">
@@ -9900,25 +9900,25 @@
         <v>439.1</v>
       </c>
       <c r="G73" s="23" t="n">
-        <v>447.54</v>
+        <v>448.18</v>
       </c>
       <c r="H73" s="24" t="n">
-        <v>482.66</v>
+        <v>482.31</v>
       </c>
       <c r="I73" s="23" t="n">
-        <v>448.5</v>
+        <v>451.82</v>
       </c>
       <c r="J73" s="23" t="n">
-        <v>426.12</v>
+        <v>425.88</v>
       </c>
       <c r="K73" s="24" t="n">
-        <v>439.55</v>
+        <v>438.12</v>
       </c>
       <c r="L73" s="23" t="n">
-        <v>452.03</v>
+        <v>451.13</v>
       </c>
       <c r="M73" s="24" t="n">
-        <v>438.98</v>
+        <v>441.88</v>
       </c>
     </row>
     <row r="74">
@@ -9932,7 +9932,7 @@
         <v>19</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>427.99</v>
+        <v>428</v>
       </c>
       <c r="E74" s="13" t="n">
         <v>422</v>
@@ -9941,25 +9941,25 @@
         <v>443</v>
       </c>
       <c r="G74" s="23" t="n">
-        <v>446.08</v>
+        <v>447.11</v>
       </c>
       <c r="H74" s="24" t="n">
-        <v>476.74</v>
+        <v>476.32</v>
       </c>
       <c r="I74" s="23" t="n">
-        <v>448.02</v>
+        <v>452.34</v>
       </c>
       <c r="J74" s="23" t="n">
-        <v>426.12</v>
+        <v>425.88</v>
       </c>
       <c r="K74" s="24" t="n">
-        <v>436.13</v>
+        <v>435.26</v>
       </c>
       <c r="L74" s="23" t="n">
-        <v>453.18</v>
+        <v>452.66</v>
       </c>
       <c r="M74" s="24" t="n">
-        <v>438.45</v>
+        <v>441.82</v>
       </c>
     </row>
     <row r="75">
@@ -9973,7 +9973,7 @@
         <v>19</v>
       </c>
       <c r="D75" s="13" t="n">
-        <v>427.99</v>
+        <v>428</v>
       </c>
       <c r="E75" s="13" t="n">
         <v>422</v>
@@ -9982,25 +9982,25 @@
         <v>443</v>
       </c>
       <c r="G75" s="23" t="n">
-        <v>440.83</v>
+        <v>442.62</v>
       </c>
       <c r="H75" s="24" t="n">
-        <v>460.19</v>
+        <v>459.72</v>
       </c>
       <c r="I75" s="23" t="n">
-        <v>440.1</v>
+        <v>453.1</v>
       </c>
       <c r="J75" s="23" t="n">
-        <v>426.31</v>
+        <v>426.16</v>
       </c>
       <c r="K75" s="24" t="n">
-        <v>433.63</v>
+        <v>433.33</v>
       </c>
       <c r="L75" s="23" t="n">
-        <v>449.91</v>
+        <v>447.65</v>
       </c>
       <c r="M75" s="24" t="n">
-        <v>436.17</v>
+        <v>436.48</v>
       </c>
     </row>
     <row r="76">
@@ -10014,7 +10014,7 @@
         <v>19</v>
       </c>
       <c r="D76" s="13" t="n">
-        <v>427.99</v>
+        <v>428</v>
       </c>
       <c r="E76" s="13" t="n">
         <v>422</v>
@@ -10023,25 +10023,25 @@
         <v>443</v>
       </c>
       <c r="G76" s="23" t="n">
-        <v>437.14</v>
+        <v>437.67</v>
       </c>
       <c r="H76" s="24" t="n">
-        <v>442.36</v>
+        <v>441.87</v>
       </c>
       <c r="I76" s="23" t="n">
-        <v>436.68</v>
+        <v>449.73</v>
       </c>
       <c r="J76" s="23" t="n">
-        <v>421.93</v>
+        <v>423.1</v>
       </c>
       <c r="K76" s="24" t="n">
-        <v>431.06</v>
+        <v>430.34</v>
       </c>
       <c r="L76" s="23" t="n">
-        <v>456.34</v>
+        <v>446.57</v>
       </c>
       <c r="M76" s="24" t="n">
-        <v>434.41</v>
+        <v>434.07</v>
       </c>
     </row>
     <row r="77">
@@ -10055,7 +10055,7 @@
         <v>19</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>427.99</v>
+        <v>428</v>
       </c>
       <c r="E77" s="13" t="n">
         <v>422</v>
@@ -10064,25 +10064,25 @@
         <v>443</v>
       </c>
       <c r="G77" s="23" t="n">
-        <v>427.64</v>
+        <v>428.21</v>
       </c>
       <c r="H77" s="24" t="n">
-        <v>430.81</v>
+        <v>430.3</v>
       </c>
       <c r="I77" s="23" t="n">
-        <v>427.33</v>
+        <v>431.25</v>
       </c>
       <c r="J77" s="23" t="n">
-        <v>418.65</v>
+        <v>418.29</v>
       </c>
       <c r="K77" s="24" t="n">
-        <v>429.19</v>
+        <v>426.76</v>
       </c>
       <c r="L77" s="23" t="n">
-        <v>436.41</v>
+        <v>433.06</v>
       </c>
       <c r="M77" s="24" t="n">
-        <v>423.48</v>
+        <v>429.34</v>
       </c>
     </row>
     <row r="78">
@@ -10105,25 +10105,25 @@
         <v>419</v>
       </c>
       <c r="G78" s="23" t="n">
-        <v>422.51</v>
+        <v>422.86</v>
       </c>
       <c r="H78" s="24" t="n">
-        <v>422.02</v>
+        <v>421.56</v>
       </c>
       <c r="I78" s="23" t="n">
-        <v>421.58</v>
+        <v>420.4</v>
       </c>
       <c r="J78" s="23" t="n">
-        <v>417.84</v>
+        <v>416.8</v>
       </c>
       <c r="K78" s="24" t="n">
-        <v>425.2</v>
+        <v>424.7</v>
       </c>
       <c r="L78" s="23" t="n">
-        <v>429.05</v>
+        <v>428.64</v>
       </c>
       <c r="M78" s="24" t="n">
-        <v>419.2</v>
+        <v>424.74</v>
       </c>
     </row>
     <row r="79">
@@ -10146,25 +10146,25 @@
         <v>419</v>
       </c>
       <c r="G79" s="23" t="n">
-        <v>415.22</v>
+        <v>414.76</v>
       </c>
       <c r="H79" s="24" t="n">
-        <v>414.9</v>
+        <v>414.41</v>
       </c>
       <c r="I79" s="23" t="n">
-        <v>416.99</v>
+        <v>414.02</v>
       </c>
       <c r="J79" s="23" t="n">
-        <v>404</v>
+        <v>403.39</v>
       </c>
       <c r="K79" s="24" t="n">
-        <v>420.03</v>
+        <v>419.81</v>
       </c>
       <c r="L79" s="23" t="n">
-        <v>420.34</v>
+        <v>417.96</v>
       </c>
       <c r="M79" s="24" t="n">
-        <v>414.64</v>
+        <v>418.5</v>
       </c>
     </row>
     <row r="80">
@@ -10187,25 +10187,25 @@
         <v>419</v>
       </c>
       <c r="G80" s="23" t="n">
-        <v>409.99</v>
+        <v>410.31</v>
       </c>
       <c r="H80" s="24" t="n">
-        <v>407.22</v>
+        <v>406.74</v>
       </c>
       <c r="I80" s="23" t="n">
-        <v>410.65</v>
+        <v>413.94</v>
       </c>
       <c r="J80" s="23" t="n">
-        <v>401.04</v>
+        <v>400.45</v>
       </c>
       <c r="K80" s="24" t="n">
-        <v>414.87</v>
+        <v>413.97</v>
       </c>
       <c r="L80" s="23" t="n">
-        <v>415.94</v>
+        <v>413.35</v>
       </c>
       <c r="M80" s="24" t="n">
-        <v>409.65</v>
+        <v>412.68</v>
       </c>
     </row>
     <row r="81">
@@ -10228,25 +10228,25 @@
         <v>419</v>
       </c>
       <c r="G81" s="23" t="n">
-        <v>407.43</v>
+        <v>407.62</v>
       </c>
       <c r="H81" s="24" t="n">
-        <v>398.99</v>
+        <v>398.5</v>
       </c>
       <c r="I81" s="23" t="n">
-        <v>410.03</v>
+        <v>413.07</v>
       </c>
       <c r="J81" s="23" t="n">
-        <v>401.04</v>
+        <v>399.98</v>
       </c>
       <c r="K81" s="24" t="n">
-        <v>412.64</v>
+        <v>412.2</v>
       </c>
       <c r="L81" s="23" t="n">
-        <v>412.29</v>
+        <v>410.87</v>
       </c>
       <c r="M81" s="24" t="n">
-        <v>408.51</v>
+        <v>409.94</v>
       </c>
     </row>
     <row r="82">
@@ -10269,25 +10269,25 @@
         <v>417</v>
       </c>
       <c r="G82" s="23" t="n">
-        <v>406.75</v>
+        <v>407.47</v>
       </c>
       <c r="H82" s="24" t="n">
-        <v>394.84</v>
+        <v>394.31</v>
       </c>
       <c r="I82" s="23" t="n">
-        <v>408.08</v>
+        <v>413.25</v>
       </c>
       <c r="J82" s="23" t="n">
-        <v>401.04</v>
+        <v>399.98</v>
       </c>
       <c r="K82" s="24" t="n">
-        <v>412.07</v>
+        <v>412.25</v>
       </c>
       <c r="L82" s="23" t="n">
-        <v>414.09</v>
+        <v>412.94</v>
       </c>
       <c r="M82" s="24" t="n">
-        <v>409.05</v>
+        <v>410.58</v>
       </c>
     </row>
     <row r="83">
@@ -10310,25 +10310,25 @@
         <v>417</v>
       </c>
       <c r="G83" s="23" t="n">
-        <v>413.46</v>
+        <v>412.8</v>
       </c>
       <c r="H83" s="24" t="n">
-        <v>401.45</v>
+        <v>400.97</v>
       </c>
       <c r="I83" s="23" t="n">
-        <v>420.54</v>
+        <v>420.51</v>
       </c>
       <c r="J83" s="23" t="n">
-        <v>402.28</v>
+        <v>400.67</v>
       </c>
       <c r="K83" s="24" t="n">
-        <v>416.62</v>
+        <v>417.39</v>
       </c>
       <c r="L83" s="23" t="n">
-        <v>422.28</v>
+        <v>419.1</v>
       </c>
       <c r="M83" s="24" t="n">
-        <v>415.88</v>
+        <v>416.57</v>
       </c>
     </row>
     <row r="84">
@@ -10351,25 +10351,25 @@
         <v>417</v>
       </c>
       <c r="G84" s="23" t="n">
-        <v>415.04</v>
+        <v>415.86</v>
       </c>
       <c r="H84" s="24" t="n">
-        <v>406.11</v>
+        <v>405.66</v>
       </c>
       <c r="I84" s="23" t="n">
-        <v>417.61</v>
+        <v>423.73</v>
       </c>
       <c r="J84" s="23" t="n">
-        <v>401.56</v>
+        <v>400.45</v>
       </c>
       <c r="K84" s="24" t="n">
-        <v>418.45</v>
+        <v>420.18</v>
       </c>
       <c r="L84" s="23" t="n">
-        <v>425.97</v>
+        <v>423.64</v>
       </c>
       <c r="M84" s="24" t="n">
-        <v>419.13</v>
+        <v>419.92</v>
       </c>
     </row>
     <row r="85">
@@ -10392,25 +10392,25 @@
         <v>417</v>
       </c>
       <c r="G85" s="23" t="n">
-        <v>419.9</v>
+        <v>419.28</v>
       </c>
       <c r="H85" s="24" t="n">
-        <v>411.82</v>
+        <v>411.34</v>
       </c>
       <c r="I85" s="23" t="n">
-        <v>426.14</v>
+        <v>421.98</v>
       </c>
       <c r="J85" s="23" t="n">
-        <v>401.78</v>
+        <v>400.68</v>
       </c>
       <c r="K85" s="24" t="n">
-        <v>420.53</v>
+        <v>422.72</v>
       </c>
       <c r="L85" s="23" t="n">
-        <v>431.08</v>
+        <v>430.65</v>
       </c>
       <c r="M85" s="24" t="n">
-        <v>426.48</v>
+        <v>426.8</v>
       </c>
     </row>
     <row r="86">
@@ -10433,25 +10433,25 @@
         <v>417</v>
       </c>
       <c r="G86" s="23" t="n">
-        <v>424.37</v>
+        <v>423.02</v>
       </c>
       <c r="H86" s="24" t="n">
-        <v>414.17</v>
+        <v>413.63</v>
       </c>
       <c r="I86" s="23" t="n">
-        <v>431.92</v>
+        <v>425.79</v>
       </c>
       <c r="J86" s="23" t="n">
-        <v>404.74</v>
+        <v>403.73</v>
       </c>
       <c r="K86" s="24" t="n">
-        <v>425.86</v>
+        <v>425.77</v>
       </c>
       <c r="L86" s="23" t="n">
-        <v>438.47</v>
+        <v>436.74</v>
       </c>
       <c r="M86" s="24" t="n">
-        <v>429.21</v>
+        <v>430.76</v>
       </c>
     </row>
     <row r="87">
@@ -10474,25 +10474,25 @@
         <v>417</v>
       </c>
       <c r="G87" s="23" t="n">
-        <v>415.14</v>
+        <v>415.22</v>
       </c>
       <c r="H87" s="24" t="n">
-        <v>404.29</v>
+        <v>403.73</v>
       </c>
       <c r="I87" s="23" t="n">
-        <v>422.26</v>
+        <v>424.05</v>
       </c>
       <c r="J87" s="23" t="n">
-        <v>401.27</v>
+        <v>400.17</v>
       </c>
       <c r="K87" s="24" t="n">
-        <v>418.33</v>
+        <v>417.64</v>
       </c>
       <c r="L87" s="23" t="n">
-        <v>426.14</v>
+        <v>423.96</v>
       </c>
       <c r="M87" s="24" t="n">
-        <v>416.85</v>
+        <v>420.06</v>
       </c>
     </row>
     <row r="88">
@@ -10515,25 +10515,25 @@
         <v>417</v>
       </c>
       <c r="G88" s="23" t="n">
-        <v>412.72</v>
+        <v>411.83</v>
       </c>
       <c r="H88" s="24" t="n">
-        <v>394.88</v>
+        <v>394.3</v>
       </c>
       <c r="I88" s="23" t="n">
-        <v>424.78</v>
+        <v>421.95</v>
       </c>
       <c r="J88" s="23" t="n">
-        <v>401.08</v>
+        <v>399.87</v>
       </c>
       <c r="K88" s="24" t="n">
-        <v>415.22</v>
+        <v>413.79</v>
       </c>
       <c r="L88" s="23" t="n">
-        <v>422.47</v>
+        <v>421.29</v>
       </c>
       <c r="M88" s="24" t="n">
-        <v>415.48</v>
+        <v>417.66</v>
       </c>
     </row>
     <row r="89">
@@ -10556,25 +10556,25 @@
         <v>417</v>
       </c>
       <c r="G89" s="23" t="n">
-        <v>406.43</v>
+        <v>406.28</v>
       </c>
       <c r="H89" s="24" t="n">
-        <v>382.21</v>
+        <v>381.67</v>
       </c>
       <c r="I89" s="23" t="n">
-        <v>415.32</v>
+        <v>416.85</v>
       </c>
       <c r="J89" s="23" t="n">
-        <v>400.51</v>
+        <v>399.56</v>
       </c>
       <c r="K89" s="24" t="n">
-        <v>411.34</v>
+        <v>411.08</v>
       </c>
       <c r="L89" s="23" t="n">
-        <v>415.03</v>
+        <v>413.12</v>
       </c>
       <c r="M89" s="24" t="n">
-        <v>411.44</v>
+        <v>412.86</v>
       </c>
     </row>
     <row r="90">
@@ -10597,25 +10597,25 @@
         <v>411.5</v>
       </c>
       <c r="G90" s="23" t="n">
-        <v>404.79</v>
+        <v>402.42</v>
       </c>
       <c r="H90" s="24" t="n">
-        <v>374.51</v>
+        <v>373.92</v>
       </c>
       <c r="I90" s="23" t="n">
-        <v>415.74</v>
+        <v>414.95</v>
       </c>
       <c r="J90" s="23" t="n">
-        <v>400</v>
+        <v>399.08</v>
       </c>
       <c r="K90" s="24" t="n">
-        <v>409.14</v>
+        <v>407.93</v>
       </c>
       <c r="L90" s="23" t="n">
-        <v>417.54</v>
+        <v>407.64</v>
       </c>
       <c r="M90" s="24" t="n">
-        <v>408.45</v>
+        <v>408.22</v>
       </c>
     </row>
     <row r="91">
@@ -10638,25 +10638,25 @@
         <v>411.5</v>
       </c>
       <c r="G91" s="23" t="n">
-        <v>402.36</v>
+        <v>401.25</v>
       </c>
       <c r="H91" s="24" t="n">
-        <v>374.02</v>
+        <v>373.47</v>
       </c>
       <c r="I91" s="23" t="n">
-        <v>416.07</v>
+        <v>411.7</v>
       </c>
       <c r="J91" s="23" t="n">
-        <v>400.03</v>
+        <v>399.07</v>
       </c>
       <c r="K91" s="24" t="n">
-        <v>407.13</v>
+        <v>406.04</v>
       </c>
       <c r="L91" s="23" t="n">
-        <v>408.28</v>
+        <v>407.6</v>
       </c>
       <c r="M91" s="24" t="n">
-        <v>405.52</v>
+        <v>406.96</v>
       </c>
     </row>
     <row r="92">
@@ -10679,25 +10679,25 @@
         <v>411.5</v>
       </c>
       <c r="G92" s="23" t="n">
-        <v>401.87</v>
+        <v>401.27</v>
       </c>
       <c r="H92" s="24" t="n">
-        <v>374.05</v>
+        <v>373.5</v>
       </c>
       <c r="I92" s="23" t="n">
-        <v>416.13</v>
+        <v>411.64</v>
       </c>
       <c r="J92" s="23" t="n">
-        <v>400.02</v>
+        <v>399.07</v>
       </c>
       <c r="K92" s="24" t="n">
-        <v>406.45</v>
+        <v>404.97</v>
       </c>
       <c r="L92" s="23" t="n">
-        <v>407.22</v>
+        <v>409.2</v>
       </c>
       <c r="M92" s="24" t="n">
-        <v>404.3</v>
+        <v>406.59</v>
       </c>
     </row>
     <row r="93">
@@ -10720,25 +10720,25 @@
         <v>411.5</v>
       </c>
       <c r="G93" s="23" t="n">
-        <v>400.83</v>
+        <v>400.86</v>
       </c>
       <c r="H93" s="24" t="n">
-        <v>370.45</v>
+        <v>369.89</v>
       </c>
       <c r="I93" s="23" t="n">
         <v>410.25</v>
       </c>
       <c r="J93" s="23" t="n">
-        <v>400.02</v>
+        <v>399.07</v>
       </c>
       <c r="K93" s="24" t="n">
-        <v>406.98</v>
+        <v>405.79</v>
       </c>
       <c r="L93" s="23" t="n">
-        <v>408.71</v>
+        <v>408.74</v>
       </c>
       <c r="M93" s="24" t="n">
-        <v>405.41</v>
+        <v>408.5</v>
       </c>
     </row>
     <row r="94">
@@ -10761,25 +10761,25 @@
         <v>406.1</v>
       </c>
       <c r="G94" s="23" t="n">
-        <v>401.04</v>
+        <v>400.03</v>
       </c>
       <c r="H94" s="24" t="n">
-        <v>369.99</v>
+        <v>369.4</v>
       </c>
       <c r="I94" s="23" t="n">
-        <v>409.11</v>
+        <v>403.82</v>
       </c>
       <c r="J94" s="23" t="n">
-        <v>400.02</v>
+        <v>398.51</v>
       </c>
       <c r="K94" s="24" t="n">
-        <v>407.79</v>
+        <v>405.69</v>
       </c>
       <c r="L94" s="23" t="n">
-        <v>409.74</v>
+        <v>410.95</v>
       </c>
       <c r="M94" s="24" t="n">
-        <v>406.4</v>
+        <v>408.96</v>
       </c>
     </row>
     <row r="95">
@@ -10802,25 +10802,25 @@
         <v>406.1</v>
       </c>
       <c r="G95" s="23" t="n">
-        <v>396.38</v>
+        <v>395.88</v>
       </c>
       <c r="H95" s="24" t="n">
-        <v>360.03</v>
+        <v>359.43</v>
       </c>
       <c r="I95" s="23" t="n">
-        <v>399.68</v>
+        <v>401.1</v>
       </c>
       <c r="J95" s="23" t="n">
-        <v>400.11</v>
+        <v>398.51</v>
       </c>
       <c r="K95" s="24" t="n">
-        <v>408.08</v>
+        <v>403.27</v>
       </c>
       <c r="L95" s="23" t="n">
-        <v>406.96</v>
+        <v>406.13</v>
       </c>
       <c r="M95" s="24" t="n">
-        <v>399.97</v>
+        <v>403.64</v>
       </c>
     </row>
     <row r="96">
@@ -10843,25 +10843,25 @@
         <v>406.1</v>
       </c>
       <c r="G96" s="23" t="n">
-        <v>399.46</v>
+        <v>398.04</v>
       </c>
       <c r="H96" s="24" t="n">
-        <v>364.16</v>
+        <v>363.6</v>
       </c>
       <c r="I96" s="23" t="n">
-        <v>404.31</v>
+        <v>399.73</v>
       </c>
       <c r="J96" s="23" t="n">
-        <v>400.11</v>
+        <v>398.51</v>
       </c>
       <c r="K96" s="24" t="n">
-        <v>407.77</v>
+        <v>402.53</v>
       </c>
       <c r="L96" s="23" t="n">
-        <v>413.69</v>
+        <v>411.98</v>
       </c>
       <c r="M96" s="24" t="n">
-        <v>403.22</v>
+        <v>408.76</v>
       </c>
     </row>
     <row r="97">
@@ -10886,25 +10886,25 @@
         <v>406.1</v>
       </c>
       <c r="G97" s="23" t="n">
-        <v>396.6</v>
+        <v>394.73</v>
       </c>
       <c r="H97" s="24" t="n">
-        <v>363.67</v>
+        <v>363.11</v>
       </c>
       <c r="I97" s="23" t="n">
-        <v>401.74</v>
+        <v>398.46</v>
       </c>
       <c r="J97" s="23" t="n">
-        <v>400.11</v>
+        <v>398.51</v>
       </c>
       <c r="K97" s="24" t="n">
-        <v>407.04</v>
+        <v>400.81</v>
       </c>
       <c r="L97" s="23" t="n">
-        <v>406.64</v>
+        <v>402.77</v>
       </c>
       <c r="M97" s="24" t="n">
-        <v>397.26</v>
+        <v>402.02</v>
       </c>
     </row>
   </sheetData>
